--- a/baslik.xlsx
+++ b/baslik.xlsx
@@ -49,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,12 @@
         <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -86,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -128,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1897,47 +1909,47 @@
       <c r="AC20" s="6" t="n"/>
     </row>
     <row r="21" ht="112.5" customHeight="1" s="13">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>video_17.mp4</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Everest'in 2.5 Katı Yüksekliğinde Bir Dağ Var — Ama Dünya'da Değil! 🌋🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Mars'taki Olympus Mons, yaklaşık 22 km yüksekliğiyle Everest'in 2.5 katı! Tabanı ise Arizona kadar geniş. Dünya'da bu dağın ağırlığı kendi kabuğunu çökerterek batmasına neden olurdu — Mars'ta kabuk buna izin veriyor!</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>bilgidozu, mars, olympusmons, uzay, geoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>Olympus Mons'un zirvesinden manzara... 🌋 Peki tırmanır mıydın? Korkanlar 1, cesurlar 2! 👇</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>NASA — Mars Facts: https://science.nasa.gov/mars/facts/</t>
         </is>
@@ -1964,47 +1976,47 @@
       <c r="AC21" s="6" t="n"/>
     </row>
     <row r="22" ht="112.5" customHeight="1" s="13">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BEKLEMEDE </t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>video_18.mp4</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>Bu Hayvanın BEYNİ YOK — Ama Görüyor, Hissediyor! ⭐🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Denizyıldızının merkezî bir beyni yok: sinir sistemi kollarına yayılmış! Her kolun ucundaki minik gözcükler ışığı algılar, binlerce ayakçık tadar, kavrar ve yürür. Kafasız ama eksiksiz — doğanın en zarif dağıtık zekâ tasarımı!</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>bilgidozu, denizyıldızı, denizcanlıları, biyoloji, ilginçbilgiler, shorts</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>Beyinsiz ama görüyor, tadıyor, yürüyor... ⭐ Doğanın en garip tasarımı mı? 1 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>Starfish: https://en.wikipedia.org/wiki/Starfish</t>
         </is>
@@ -2031,47 +2043,47 @@
       <c r="AC22" s="6" t="n"/>
     </row>
     <row r="23" ht="112.5" customHeight="1" s="13">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>video_19.mp4</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>Yunuslar Tek Gözü Açık Uyur! 🐬😴 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Yunusun beyninin iki yarısı sırayla uyur: bir yarı derin uykudayken diğeri düşman nöbeti tutar, yüzer ve nefes aldırır! Göz de beynin uyuyan tarafına göre kapanır. Adı: yarım küre uykusu (USWS) — doğanın nöbetçi sistemi!</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>bilgidozu, yunus, hayvanlaralemi, uyku, deniz, bilim, shorts</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>Yunus bile nöbet tutarak uyurken sen nasıl uyuyorsun? 😄🐬 Uykucular 1 yazsın!</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>Sleep Foundation — Animals and Sleep: https://www.sleepfoundation.org/animals-and-sleep</t>
         </is>

--- a/baslik.xlsx
+++ b/baslik.xlsx
@@ -530,7 +530,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC112"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="13" min="1" max="1"/>
     <col width="22.86" customWidth="1" style="13" min="2" max="2"/>
@@ -3504,54 +3504,62 @@
       <c r="AC39" s="6" t="n"/>
     </row>
     <row r="40" ht="112.5" customHeight="1" s="13">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BEKLEMEDE </t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>video_33.mp4</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>Kendini Neden Gıdıklayamazsın? Beynin Hamleni Önceden Biliyor! 🧠🤭 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Başka biri dokunduğunda kolayca gıdıklanırken kendi kendini gıdıklayamamanın sebebi beyinciktir! Beyincik, kendi el hareketini saliseler öncesinden tahmin ederek duyusal kortekse 'bu tehdit değil, kendi dokunuşun' sinyali gönderir ve gıdıklanma tepkisini otomatik olarak bastırır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #psikoloji</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>bilgidozu, gıdıklanma, beyin, beyincik, nörobilim, psikoloji, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>Biri dokununca çok gıdıklananlardan mısın? 😄🤭 Evet diyenler '1', bana işlemez diyenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>Wikipedia — Tickling (Self-tickling): https://en.wikipedia.org/wiki/Tickling</t>
         </is>
       </c>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/sh9zYFybcHY</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-23 21:24</t>
+        </is>
+      </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="6" t="n"/>
       <c r="N40" s="6" t="n"/>
@@ -8414,6 +8422,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8429,136 +8438,136 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>İşçi Adı</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>Son Güncelleme Zamanı</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>Son Hata Mesajı</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Kaç İş Yaptı</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Son İşlem Özeti</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Yükleyici (Drive -&gt; YouTube)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Çalışıyor</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 18:29</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
+      <c r="D2" s="0" t="inlineStr"/>
+      <c r="E2" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>video_32.mp4 yayınlandı (https://youtu.be/mANNR6Tf21o)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Yorumcu &amp; Kapak İşçisi (OAuth)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Çalışıyor</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
+      <c r="D3" s="0" t="inlineStr"/>
+      <c r="E3" s="0" t="n">
         <v>54</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Tam yetkili OAuth (youtube.force-ssl + drive + sheets) bağlandı ve aktif</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Analitik Çekici (YouTube API)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Çalışıyor</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
+      <c r="D4" s="0" t="inlineStr"/>
+      <c r="E4" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>58 videonun gerçek görüntülenme (33457) ve yorum verisi çekildi</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Telegram Bildirim İşçisi</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Çalışıyor</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 18:29</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
+      <c r="D5" s="0" t="inlineStr"/>
+      <c r="E5" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>video_32.mp4 yayın kartı ve sabit yorum metni gönderildi</t>
         </is>
@@ -8579,108 +8588,108 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Kontrol Noktası</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>Seviye</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>Son Kontrol</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Detay ve Çözüm</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>YouTube API Günlük Kotası</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Sorunsuz</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Yeşil</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Günlük 10.000 birim kotası aktif ve yeterli.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Google Drive &amp; Sheets Senkronu</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Sorunsuz</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>Yeşil</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Drive video klasörü (82 dosya) ve 3 sekmeli yükleme tablosu canlı bağlı.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Yorum &amp; Kapak İşçisi (force-ssl)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Sorunsuz</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>Yeşil</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>2026-10-23 21:15</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>youtube.force-ssl yetkisi onaylandı; otomatik ilk yorum ve kapak giydirme hazır.</t>
         </is>

--- a/baslik.xlsx
+++ b/baslik.xlsx
@@ -529,8 +529,8 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC112"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <dimension ref="A1:AC133"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="13" min="1" max="1"/>
     <col width="22.86" customWidth="1" style="13" min="2" max="2"/>
@@ -8221,27 +8221,1065 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="112.5" customHeight="1" s="13"/>
-    <row r="114" ht="112.5" customHeight="1" s="13"/>
-    <row r="115" ht="112.5" customHeight="1" s="13"/>
-    <row r="116" ht="112.5" customHeight="1" s="13"/>
-    <row r="117" ht="112.5" customHeight="1" s="13"/>
-    <row r="118" ht="112.5" customHeight="1" s="13"/>
-    <row r="119" ht="112.5" customHeight="1" s="13"/>
-    <row r="120" ht="112.5" customHeight="1" s="13"/>
-    <row r="121" ht="112.5" customHeight="1" s="13"/>
-    <row r="122" ht="112.5" customHeight="1" s="13"/>
-    <row r="123" ht="112.5" customHeight="1" s="13"/>
-    <row r="124" ht="112.5" customHeight="1" s="13"/>
-    <row r="125" ht="112.5" customHeight="1" s="13"/>
-    <row r="126" ht="112.5" customHeight="1" s="13"/>
-    <row r="127" ht="112.5" customHeight="1" s="13"/>
-    <row r="128" ht="112.5" customHeight="1" s="13"/>
-    <row r="129" ht="112.5" customHeight="1" s="13"/>
-    <row r="130" ht="112.5" customHeight="1" s="13"/>
-    <row r="131" ht="112.5" customHeight="1" s="13"/>
-    <row r="132" ht="112.5" customHeight="1" s="13"/>
-    <row r="133" ht="112.5" customHeight="1" s="13"/>
+    <row r="113" ht="112.5" customHeight="1" s="13">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>video_101.mp4</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>Güneş Bir Saniyeliğine Sönseydi Ne Olurdu? ☀️🌑 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>Şu an başını kaldırıp gökyüzüne baktığında, Güneş'in hâlâ orada olduğundan gerçekten emin misin? Ya tam şu saniye sessizce söndüyse? İşin en ürpertici kısmı ne biliyor musun? Bunu tam sekiz dakika yirmi saniye boyunca ruhun bile duymayacak. Çünkü Güneş'ten çıkan son ışık gözüne ulaşana kadar gökyüzü masmavi kalır. Ama sekizinci dakikanın sonunda gökyüzü bir anda zifiri karanlığa gömülür ve Dünya yörüngeden kopup buzlu boşluğa savrulur. Peki sen o son sekiz dakikayı dışarıda gökyüzünü izleyerek mi geçirirdin, yoksa yeraltı sığınaklarına inerek mi? Yorumlarda buluşalım.
+Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Sunlight
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, güneş, uzay, kozmik felaket, astronomi, bilim, dünya, ışık hızı, ilginç bilgiler, shorts</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H113" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sunlight</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="112.5" customHeight="1" s="13">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>video_102.mp4</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>Ay Dünya'ya Yaklaşsaydı Okyanuslara Ne Olurdu? 🌕🌊 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>Gece gökyüzüne baktığında, Ay'ın hep aynı yerde durduğunu sanıyorsun değil mi? Peki ya Ay Dünya'ya doğru yaklaşmaya başlasaydı ne olurdu? İlk başta gökyüzünde devasa görünürdü ama hemen ardından kütle çekim kabusu başlardı. Okyanuslar yüzlerce metre yükselip kıyı şehirlerini yutardı. Dünya'ya on sekiz bin kilometre mesafedeki Roche sınırına girdiği anda ise Ay gökyüzünde paramparça olur ve Dünya'nın etrafında tıpkı Satürn gibi parlak bir halka oluştururdu. Peki sen gökyüzünde Satürn gibi dev bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım.
+Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Roche_limit
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, ay, dünya, roche sınırı, satürn, uzay, astronomi, bilim, kozmik felaket, shorts</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Roche_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="112.5" customHeight="1" s="13">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>video_103.mp4</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>Uzayda Ağlarsan Gözyaşların Neden Yanağından Akmaz? 🧑‍🚀💧 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>Uzayda tek başına süzülürken bir anda ağlamaya başlasan gözyaşlarının yanağından aşağı süzüleceğini mi sanıyorsun? Hiç de öyle olmaz. Dünya'da gözyaşını aşağı çeken şey yerçekimidir. Ama uzayın ağırlıksız boşluğunda, su moleküllerini birbirine kenetleyen yüzey gerilimi tek patron haline gelir. Gözünden çıkan her damla, akmak yerine göz pınarının tam üzerinde şeffaf, titreyen bir su küresine dönüşür ve sen bir bezle silene kadar yüzünden asla ayrılmaz. Peki sen yerçekimsiz ortamda yaşamayı deneyimlemek mi isterdin, yoksa ayağının yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım.
+Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Surface_tension
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F115" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, uzay, astronot, yerçekimi, yüzey gerilimi, bilim, fizik, uzay istasyonu, ilginç bilgiler, shorts</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H115" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I115" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Surface_tension</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="112.5" customHeight="1" s="13">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>video_104.mp4</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>Dünya'ya 50 Işık Yılı Mesafede Süpernova Patlasa Ne Olur? 💥🌟 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>Gündüz vakti masmavi gökyüzünde bir anda ikinci bir Güneş'in parladığını hayal et. Dünya'ya elli ışık yılı mesafede dev bir yıldız süpernova olarak patlasaydı tam olarak bunu yaşardık. Haftalarca geceleri bile gökyüzü hiç kararmazdı. Ama asıl tehlike o parlak ışık değil, görünmez gama ışınları olurdu. Üst atmosferdeki ozon tabakası hızla erir ve yüzeye inen radyasyon okyanuslardaki besin zincirini altüst ederdi. Peki böyle bir kozmik patlama görsen, önce teleskopla izlemeye mi koşardın yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım.
+Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Near-Earth_supernova
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, süpernova, uzay, gama ışınları, kozmik felaket, yıldız, astronomi, bilim, dünya, shorts</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="112.5" customHeight="1" s="13">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>video_105.mp4</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>Bir Çay Kaşığı Nötron Yıldızı Dünya'ya Düşse Ne Olur? 🥄🌌 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>Elindeki küçücük bir çay kaşığının Everest Dağı kadar ağır olabileceğini hayal edebilir misin? Evrenin en ekstrem canavarı olan nötron yıldızlarıyla tanış. Dev bir yıldız çöktüğünde çekirdeği o kadar korkunç sıkışır ki, koca bir Güneş sadece yirmi kilometre çapında bir küreye hapsolur. Bu yıldızdan alacağın tek bir çay kaşığı madde tam bir milyar ton ağırlığındadır. Onu Dünya'da elinden bıraksan toprağı ve kayaları delip doğrudan gezegenin çekirdeğine kadar batardı. Peki seni uzayda en çok büyüleyen şey, kara delikler mi yoksa nötron yıldızları mı? Yorumlarda buluşalım.
+Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Neutron_star
+🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #uzay #bilim</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, nötron yıldızı, kara delik, uzay, astronomi, fizik, bilim, evren, ilginç bilgiler, shorts</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="inlineStr">
+        <is>
+          <t>Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H117" s="14" t="inlineStr">
+        <is>
+          <t>Uzay ve Astronomi</t>
+        </is>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Neutron_star</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="112.5" customHeight="1" s="13">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>video_106.mp4</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>Kendi Sesini Kayıtta Dinleyince Neden Tuhaf Gelir? 🎙️🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>Bir ses kaydında kendi sesini duyduğun an “Bu gerçekten benim sesim mi?” diye yüzünü buruşturduğun oldu mu? Merak etme, yalnız değilsin. Sen konuşurken sesini iki farklı yoldan aynı anda duyarsın. Hem havadan kulağına gelen dalgalarla, hem de ses tellerinin kafatası kemiklerini titreştirerek iç kulağına gönderdiği kemik iletimiyle. Kafatası kemiklerin bas frekansları güçlendirdiği için kendi sesini hep daha tok ve derin algılarsın. Ama kayıtta, kemik iletimi devreden çıkar ve başkalarının duyduğu o gerçek sesine yüzleşirsin. Peki sen kayıtlarda kendi sesini dinlemeye alışabildin mi, yoksa duyunca hemen kapatıyor musun? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/Bone_conduction</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bone_conduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="112.5" customHeight="1" s="13">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>video_107.mp4</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Yüksek Bir Yerden Bakınca Beyin Neden 'Atla' Diye Fısıldar? 🧗‍♂️🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>Yüksek bir balkonun ya da uçurumun kenarından aşağı baktığında içinde hiçbir kötü niyet yokken bile bir anda “Ya şimdi atlarsam” diye ürpertici bir düşünce geçti mi? Fransızların “boşluğun çağrısı” dediği bu durum aslında beyninin aşırı hızlı çalışan bir hayatta kalma alarmıdır. Beynin kenara yaklaştığında denge merkezine “Geri çekil, tehlikedesin” sinyali gönderir. Bilinçli zihnin ise bu ani geri çekilme refleksini sanki aşağı atlamak istemişim de kendimi zor tutmuşum gibi yanlış yorumlar. Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H119" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="112.5" customHeight="1" s="13">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>video_108.mp4</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>Acı Biber Aslında Ağzını Yakmaz — Beynini Nasıl Kandırır? 🌶️🔥 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>Çok acı bir biber ısırdığında ağzının alev alev yandığını hissediyorsun ya, sana dilinin aslında hiç yanmadığını, tamamen beyninin kandırıldığını söylesem? Biberin içindeki kapsaisin molekülü dokularına fiziksel bir zarar vermez. Sadece dilindeki 43 derecenin üzerindeki sıcaklıklarda açılan ısı alıcılarına gizlice kilitlenir ve beynine ağzın kaynar suyla yanıyor diye sahte bir alarm gönderir. Üstelik kapsaisin suda çözünmediği için su içmek yangını ağzının her yerine yayar. Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa ayrana koşmak mı? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/Capsaicin</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa yoğurt ve ayrana koşmak mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I120" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Capsaicin</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="112.5" customHeight="1" s="13">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>video_109.mp4</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>Soğukta Dişlerin Neden İrade Dışı Takırdar? 🥶🦷 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>Dondurucu bir soğukta dışarı çıktığında, ne kadar sıkmaya çalışırsan çalış, dişlerinin kendi kendine takırdadığı oldu mu? Bunu durduramazsın. Çünkü o an kontrol beynindeki hipotalamus adlı gizli termostata geçer. İç sıcaklığın milimetrik olarak düştüğü anda, beynin kaslarını saniyede defalarca kasılıp gevşemeye zorlayarak acil ısı üretir. Çene kasların vücudunun en güçlü ve beynine en yakın kas grubu olduğu için bu titreme en şiddetli orada hissedilir ve dişlerin birbirine vurur. Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/Shivering</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa kavurucu yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H121" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Shivering</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="112.5" customHeight="1" s="13">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>video_110.mp4</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Utandığında Neden Sadece Yüzün ve Kulakların Kızarır? 😳🧠 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>Herkesin içinde bir anda utandığında neden kolların değil de sadece yanakların ve kulakların alev alev kızarır? Üstelik sakın kızarma dedikçe daha da kıpkırmızı olursun. Charles Darwin'in tüm duyguların en insaniye olanı dediği bu tepki vücudunun gizli dürüstlük mekanizmasıdır. Utandığın saniye beynin ani bir adrenalin salgılar ve sadece yüzündeki özel kılcal damarlar genişleyerek cildinin altına sıcak kan hücum eder. Evrimsel olarak bu tek kelime etmeden çevrendekilere hata yaptım ve farkındayım demenin sessiz yoludur. Peki sen utandığında sakin kalabilenlerden misin, yoksa saniyesinde kızaranlardan mı? Yorumlarda buluşalım.
+Kaynak: https://en.wikipedia.org/wiki/Blushing</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>Nörobilim ve İnsan Bedeni</t>
+        </is>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Blushing</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="112.5" customHeight="1" s="13">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>video_111.mp4</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>Dünya'nın En Issız Noktası Point Nemo: En Yakın İnsanlar Uzayda! 🌊🛰️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>Dünya üzerinde öyle ıssız bir nokta var ki, orada bir tekneyle mahsur kalsan sana en yakın insanlar Dünya'da değil, uzayda olurdu. Güney Pasifik Okyanusu'nun ortasındaki Point Nemo ile tanış. Burası en yakın kara parçasına tam 2.688 kilometre uzaklıktadır. Buna karşılık, Uluslararası Uzay İstasyonu başının sadece 400 kilometre üzerinden geçer. Yani gökyüzündeki astronotlar, sana karadaki insanlardan tam 6 kat daha yakındır. Uzay ajansları da ömrü biten uyduları bu dev su mezarlığına düşürür. Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Pole_of_inaccessibility
+#bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, point nemo, güney pasifik, dünyanın en ıssız noktası, uydu mezarlığı, uluslararası uzay istasyonu, coğrafya, doğa, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="112.5" customHeight="1" s="13">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>video_112.mp4</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Antarktika'daki Buzuldan Neden Kan Kırmızısı Şelale Akıyor? 🧊🩸 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>Antarktika'nın bembeyaz, dondurucu buzullarının arasından bir anda kıpkırmızı, kan renginde bir şelalenin aktığını görsen ne düşünürdün? Taylor Buzulu'ndaki bu ürpertici manzaranın sebebi kan ya da yosun değil, tam 5 milyon yıl önce buzulun 400 metre altına hapsolmuş antik bir yeraltı gölü. Bu gizli gölün suyu okyanuslardan 3 kat daha tuzlu olduğu için dondurucu soğukta bile asla donmuyor. İçindeki yoğun demir, buzulun çatlaklarından sızıp milyonlarca yıl sonra ilk kez havadaki oksijenle temas ettiği anda saniyeler içinde paslanarak kıpkırmızı bir şelaleye dönüşüyor. Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Blood_Falls
+#bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, kan şelalesi, blood falls, antarktika, taylor buzulu, doğa olayları, coğrafya, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Blood_Falls</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="112.5" customHeight="1" s="13">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>video_113.mp4</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>5,5 Milyon Yıldır Güneş Görmeyen Mühürlü Mağara: Movile! 🕳️🕷️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>Tam 5,5 milyon yıl boyunca güneş ışığının tek bir zerresini bile görmemiş, mühürlü bir yeraltı dünyasının kapısını açtığını hayal et. Romanya'da tesadüfen keşfedilen Movile Mağarası, dış dünyadan tamamen kopuk bambaşka bir gezegen gibi. İçerideki havada oksijen normalin yarısından bile az, atmosferi ise zehirli hidrojen sülfür ve karbondioksitle dolu. Güneş ışığı olmadığı için buradaki yaşam tamamen kimyasal enerjiyle ayakta kalıyor ve içeride gözleri yok olmuş, sadece buraya özgü 30'dan fazla gizemli canlı türü yaşıyor. Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Movile_Cave
+#bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, movile mağarası, mühürlü mağara, romanya, kemosentez, gizemli yerler, doğa, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Movile_Cave</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="112.5" customHeight="1" s="13">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>video_114.mp4</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>Dallol Volkanı: Dünya Üzerindeki En Asidik ve Renkli Cehennem! 🌋🧪 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>Şu gördüğün neon sarısı ve zümrüt yeşili göller başka bir gezegene değil, Dünya üzerindeki en tehlikeli cehenneme ait. Etiyopya'daki Danakil Çöküntüsü'nde yer alan Dallol Volkanı, deniz seviyesinin 48 metre altında kaynayan dev bir kimya laboratuvarı gibidir. Yerin altındaki kızgın magma, kalın tuz ve kükürt yataklarıyla buluştuğunda, yüzeye akü asidinden bile daha yakıcı kaynar sular ve zehirli klor gazları fışkırır. Burada maskesiz uzun süre nefes almak bile imkânsızdır. Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)
+#bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, dallol volkanı, danakil çöküntüsü, etiyopya, asit gölleri, ekstrem doğa, coğrafya, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="112.5" customHeight="1" s="13">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>video_115.mp4</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>Yerin 2.224 Metre Altında Ne Var? Dünya'nın En Derin Mağarası! 🧗‍♂️🌑 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>Yerin tam 2.224 metre altına, yani üst üste dizilmiş 7 Eyfel Kulesi derinliğine karanlık bir kuyudan indiğini hayal et. Kafkas Dağları'ndaki Krubera Mağarası, Dünya'nın bilinen en derin uçurumlarından biridir. Buraya inen mağaracıların en dibe ulaşması haftalar sürer ve içeride yeraltı şelaleleriyle buz gibi su tünelleri vardır. En şaşırtıcı olanı ise, 2.000 metre derinlikteki o dondurucu ve ışıksız sularda bile dış dünyayı hiç görmemiş şeffaf canlıların yaşamaya devam etmesidir. Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım!
+Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
+Kaynak: https://en.wikipedia.org/wiki/Krubera_Cave
+#bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="inlineStr">
+        <is>
+          <t>bilgidozu, krubera mağarası, dünyanın en derin mağarası, kafkas dağları, mağaracılık, doğa, coğrafya, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="inlineStr">
+        <is>
+          <t>Doğa ve Hayvanlar</t>
+        </is>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Krubera_Cave</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="112.5" customHeight="1" s="13">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>video_116.mp4</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>2.100 Yıllık Batıktan Çıkan İlk Analog Bilgisayar: Antikythera! ⚙️🏛️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>Denizin dibinde iki bin yıl boyunca paslanmış bir Yunan batığından, modern saatler kadar karmaşık dişlilere sahip antik bir bilgisayar çıktığını biliyor muydun?
+Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Antikythera_mechanism
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F128" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H128" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="112.5" customHeight="1" s="13">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>video_117.mp4</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>Derinkuyu Yeraltı Şehri: 20 Bin Kişi Yerin Altında Nasıl Nefes Aldı? 🏺🕯️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>Kapadokya'nın altında, yirmi bin insanın hayvanları ve erzaklarıyla birlikte haftalarca hiç yeryüzüne çıkmadan yaşayabildiği sekiz katlı dev bir yeraltı şehri var: Derinkuyu.
+Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Derinkuyu_underground_city
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F129" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H129" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="112.5" customHeight="1" s="13">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>video_118.mp4</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>Voynich El Yazması: 600 Yıldır Kimsenin Okuyamadığı Şifreli Kitap! 📜🔍 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>Dünyanın en iyi şifre çözücüleri, dilbilimcileri ve yapay zekâları bir araya geldi ama altı yüz yıllık bu kitabın tek bir cümlesini bile okuyamadı: Voynich El Yazması.
+Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Voynich_manuscript
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F130" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H130" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Voynich_manuscript</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="112.5" customHeight="1" s="13">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>video_119.mp4</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>Puma Punku H-Blokları: Jilet Bile Girmeyen Antik Taşların Sırrı! 🪨📐 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>Deniz seviyesinden üç bin sekiz yüz metre yüksekte, aralarına jilet bile girmeyecek kadar kusursuz kesilmiş yüz tonluk taş bloklar düşün: Puma Punku.
+Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Pumapunku
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F131" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H131" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pumapunku</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="112.5" customHeight="1" s="13">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>video_120.mp4</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>Babil'in Asma Bahçeleri Gerçekte Babil'de Değil Miydi? 🌿🏛️ #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>Dünyanın Yedi Harikası'ndan biri sayılan Babil'in Asma Bahçeleri'nin aslında hiçbir zaman Babil'de olmadığını duysan ne derdin?
+Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #tarih #arkeoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F132" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H132" s="14" t="inlineStr">
+        <is>
+          <t>Tarih ve Antik Mühendislik</t>
+        </is>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="112.5" customHeight="1" s="13">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>uzun_video_13.mp4</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>Beyninin Senden Gizlediği 3 Otomatik Hile (Kendi Sesin, Boşluğun Çağrısı ve Sahte Acı) 🧠🔒 #bilgidozu</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>Beyninin senden gizlediği 3 otomatik hileyi tek bir merak yolculuğunda inceliyoruz:
+1 · Kendi Sesin Neden Kayıtta Yabancı Gelir? (Kafatası Kemik İletimi)
+2 · Yüksek Bir Yerden Bakınca Beyin Neden 'Atla' Diye Fısıldar? (Boşluğun Çağrısı)
+3 · Acı Biber Aslında Ağzını Yakmaz — Beynini Nasıl Kandırır? (Kapsaisin &amp; TRPV1)
+Bu 3 beyin hilesinden seni en çok şaşırtan hangisi oldu: Kendi sesinin kemik iletimi mi, yüksek yerdeki Boşluğun Çağrısı mı, yoksa acı biberin sahte yanık alarmı mı? Yorumlarda buluşalım! 👇
+📚 Kaynaklar:
+https://en.wikipedia.org/wiki/Bone_conduction
+https://en.wikipedia.org/wiki/The_imp_of_the_perverse
+https://en.wikipedia.org/wiki/Capsaicin
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
+        <is>
+          <t>#bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="inlineStr">
+        <is>
+          <t>bilgi dozu, nörobilim, psikoloji, insan beyni, kemik iletimi, kapsaisin, bilim, belgesel</t>
+        </is>
+      </c>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>Bu 3 beyin hilesinden seni en çok şaşırtan hangisi oldu: Kendi sesinin kemik iletimi mi, yüksek yerdeki Boşluğun Çağrısı mı, yoksa acı biberin sahte yanık alarmı mı? Yorumlarda buluşalım! 👇</t>
+        </is>
+      </c>
+      <c r="H133" s="14" t="inlineStr">
+        <is>
+          <t>Uzun — Nörobilim ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I133" s="14" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bone_conduction
+https://en.wikipedia.org/wiki/The_imp_of_the_perverse
+https://en.wikipedia.org/wiki/Capsaicin</t>
+        </is>
+      </c>
+    </row>
     <row r="134" ht="112.5" customHeight="1" s="13"/>
     <row r="135" ht="112.5" customHeight="1" s="13"/>
     <row r="136" ht="112.5" customHeight="1" s="13"/>

--- a/baslik.xlsx
+++ b/baslik.xlsx
@@ -530,7 +530,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC133"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="13" min="1" max="1"/>
     <col width="22.86" customWidth="1" style="13" min="2" max="2"/>
@@ -3582,7 +3582,7 @@
     <row r="41" ht="112.5" customHeight="1" s="13">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>BEKLEMEDE</t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -3626,8 +3626,16 @@
           <t>Wikipedia — Hypnic jerk: https://en.wikipedia.org/wiki/Hypnic_jerk</t>
         </is>
       </c>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tCuQNw_V74I</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-24 14:24</t>
+        </is>
+      </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="6" t="n"/>
       <c r="N41" s="6" t="n"/>
@@ -9520,16 +9528,16 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 18:29</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr"/>
       <c r="E2" s="0" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>video_32.mp4 yayınlandı (https://youtu.be/mANNR6Tf21o)</t>
+          <t>video_34.mp4 yayınlandı (https://youtu.be/tCuQNw_V74I)</t>
         </is>
       </c>
     </row>
@@ -9546,16 +9554,16 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr"/>
       <c r="E3" s="0" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Tam yetkili OAuth (youtube.force-ssl + drive + sheets) bağlandı ve aktif</t>
+          <t>video_34.mp4 sabit yorumu otomatik atıldı (ID: Ugzvwaj5XgX3cgIfA8R4AaABAg)</t>
         </is>
       </c>
     </row>
@@ -9572,16 +9580,16 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr"/>
       <c r="E4" s="0" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>58 videonun gerçek görüntülenme (33457) ve yorum verisi çekildi</t>
+          <t>34.276 görüntülenme ve 494 beğeni verisi çekildi</t>
         </is>
       </c>
     </row>
@@ -9598,16 +9606,16 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 18:29</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr"/>
       <c r="E5" s="0" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>video_32.mp4 yayın kartı ve sabit yorum metni gönderildi</t>
+          <t>video_34.mp4 yayın kartı ve sabit yorum metni gönderildi</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9678,7 @@
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
@@ -9697,12 +9705,12 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>Drive video klasörü (82 dosya) ve 3 sekmeli yükleme tablosu canlı bağlı.</t>
+          <t>Ana Drive klasörü (1MBjwKp1DXoxLiCAkds84MowZAFMOK7Br), KAPAKLAR klasörü ve 3 sekmeli baslik.xlsx canlı bağlı.</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9732,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>2026-10-23 21:15</t>
+          <t>2026-10-24 14:24</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">

--- a/baslik.xlsx
+++ b/baslik.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="I2" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Venus: https://science.nasa.gov/venus/</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I3" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>The Conversation (UW 5 yıllık maske deneyi): https://theconversation.com/never-cross-a-crow-it-will-remember-your-face-2121</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="I4" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Banana Equivalent Dose: https://en.wikipedia.org/wiki/Banana_equivalent_dose</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Mikorizal ağ (Wood Wide Web): https://en.wikipedia.org/wiki/Mycorrhizal_network</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="I6" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Stars: https://science.nasa.gov/universe/stars/</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NOAA — Why is the ocean blue: https://oceanservice.noaa.gov/facts/oceanblue.html</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="I8" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>The Conversation (RMIT araştırmacıları): https://theconversation.com/bees-join-an-elite-group-of-species-that-understands-the-concept-of-zero-as-a-number-97316 RMIT: https://www.rmit.edu.au/news/all-news/2018/jun/honeybees-zero-in-on-nothing</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>phys.org (PNAS 2022): https://phys.org/news/2022-09-earth-harbours-ants-wild-birds.html</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Europa: https://science.nasa.gov/jupiter/moons/europa/</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>MIT News (2023 Roma betonu): https://news.mit.edu/2023/roman-concrete-durability-lime-casts-0106</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>SLAC (2017 elmas yağmuru deneyi): https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Tardigrada: https://en.wikipedia.org/wiki/Tardigrade</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Psychology Today (30+ çalışma meta-analizi): https://www.psychologytoday.com/us/blog/best-practices-in-health/202506/eyes-wide-open-what-your-eyes-reveal-about-attraction Yedek: https://www.medicalnewstoday.com/articles/dilated-pupils-meaning</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="I15" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>USDA Forest Service — Pando: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I16" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NOAA / NWS — Lightning Science: https://www.weather.gov/safety/lightning-science</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1879,9 +1879,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>NASA Venus: https://science.nasa.gov/venus/
-SLAC elmas yağmuru: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets
-NASA Europa: https://science.nasa.gov/jupiter/moons/europa/</t>
+          <t>NASA Venus: https://science.nasa.gov/venus/ SLAC elmas yağmuru: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets NASA Europa: https://science.nasa.gov/jupiter/moons/europa/</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1967,9 +1965,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>The Conversation karga: https://theconversation.com/never-cross-a-crow-it-will-remember-your-face-2121
-The Conversation arılar: https://theconversation.com/bees-join-an-elite-group-of-species-that-understands-the-concept-of-zero-as-a-number-97316
-USDA Pando: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
+          <t>The Conversation karga: https://theconversation.com/never-cross-a-crow-it-will-remember-your-face-2121 The Conversation arılar: https://theconversation.com/bees-join-an-elite-group-of-species-that-understands-the-concept-of-zero-as-a-number-97316 USDA Pando: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -2055,9 +2051,7 @@
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>Görünmez Goril: https://en.wikipedia.org/wiki/The_Invisible_Gorilla
-Kapı Eşiği Etkisi: https://en.wikipedia.org/wiki/Doorway_effect
-Özgür İrade Nörobilimi: https://en.wikipedia.org/wiki/Neuroscience_of_free_will</t>
+          <t>Görünmez Goril: https://en.wikipedia.org/wiki/The_Invisible_Gorilla Kapı Eşiği Etkisi: https://en.wikipedia.org/wiki/Doorway_effect Özgür İrade Nörobilimi: https://en.wikipedia.org/wiki/Neuroscience_of_free_will</t>
         </is>
       </c>
       <c r="J19" s="5" t="n"/>
@@ -2124,7 +2118,7 @@
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Jupiter Facts: https://science.nasa.gov/jupiter/facts/</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -2203,7 +2197,7 @@
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Mars Facts: https://science.nasa.gov/mars/facts/</t>
         </is>
       </c>
       <c r="J21" s="5" t="n"/>
@@ -2270,7 +2264,7 @@
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Starfish: https://en.wikipedia.org/wiki/Starfish</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -2349,7 +2343,7 @@
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Sleep Foundation — Animals and Sleep: https://www.sleepfoundation.org/animals-and-sleep</t>
         </is>
       </c>
       <c r="J23" s="5" t="n"/>
@@ -2376,7 +2370,7 @@
     <row r="24" ht="112.5" customHeight="1" s="13">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEKLEMEDE </t>
+          <t>YÜKLENDİ</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -2416,7 +2410,7 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ (https://youtu.be/MzkXjFsAZ90)</t>
+          <t>NASA — Saturn Facts: https://science.nasa.gov/saturn/facts/</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -2495,7 +2489,7 @@
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Human Microbiome: https://en.wikipedia.org/wiki/Human_microbiome</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -2574,7 +2568,7 @@
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Glass (cam bir katıdır): https://en.wikipedia.org/wiki/Glass</t>
         </is>
       </c>
       <c r="J26" s="5" t="n"/>
@@ -2641,7 +2635,7 @@
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Moon Facts: https://science.nasa.gov/moon/facts/</t>
         </is>
       </c>
       <c r="J27" s="5" t="n"/>
@@ -2708,7 +2702,7 @@
       </c>
       <c r="I28" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Cat communication (miyav): https://en.wikipedia.org/wiki/Cat_communication</t>
         </is>
       </c>
       <c r="J28" s="5" t="n"/>
@@ -2775,7 +2769,7 @@
       </c>
       <c r="I29" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Earth Facts: https://science.nasa.gov/earth/facts/</t>
         </is>
       </c>
       <c r="J29" s="5" t="n"/>
@@ -2842,7 +2836,7 @@
       </c>
       <c r="I30" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Honey (raf ömrü): https://en.wikipedia.org/wiki/Honey</t>
         </is>
       </c>
       <c r="J30" s="5" t="n"/>
@@ -2909,7 +2903,7 @@
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Earth's inner core: https://en.wikipedia.org/wiki/Earth%27s_inner_core</t>
         </is>
       </c>
       <c r="J31" s="5" t="n"/>
@@ -2976,7 +2970,7 @@
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Elephant cognition (sismik iletişim): https://en.wikipedia.org/wiki/Elephant_cognition</t>
         </is>
       </c>
       <c r="J32" s="5" t="n"/>
@@ -3043,7 +3037,7 @@
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>NASA — Uranus Facts: https://science.nasa.gov/uranus/facts/</t>
         </is>
       </c>
       <c r="J33" s="5" t="n"/>
@@ -3110,7 +3104,7 @@
       </c>
       <c r="I34" s="18" t="inlineStr">
         <is>
-          <t>YÜKLENDİ / ATLANDI (31'den Başlatma Kilidi)</t>
+          <t>Ten percent of brain myth: https://en.wikipedia.org/wiki/Ten_percent_of_brain_myth</t>
         </is>
       </c>
       <c r="J34" s="5" t="n"/>
@@ -3178,8 +3172,7 @@
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>NASA Mars Facts: https://science.nasa.gov/mars/facts/
-NASA Neptune Facts (rüzgarlar): https://science.nasa.gov/neptune/facts/</t>
+          <t>NASA Mars Facts: https://science.nasa.gov/mars/facts/ NASA Neptune Facts (rüzgarlar): https://science.nasa.gov/neptune/facts/</t>
         </is>
       </c>
       <c r="J35" s="5" t="n"/>
@@ -3247,9 +3240,7 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>Turritopsis dohrnii (ölümsüz denizanası): https://en.wikipedia.org/wiki/Turritopsis_dohrnii
-Sleep Foundation (USWS): https://www.sleepfoundation.org/animals-and-sleep
-PBS NOVA (köpek koku): https://www.pbs.org/wgbh/nova/article/dogs-sense-of-smell/</t>
+          <t>Turritopsis dohrnii (ölümsüz denizanası): https://en.wikipedia.org/wiki/Turritopsis_dohrnii Sleep Foundation (USWS): https://www.sleepfoundation.org/animals-and-sleep PBS NOVA (köpek koku): https://www.pbs.org/wgbh/nova/article/dogs-sense-of-smell/</t>
         </is>
       </c>
       <c r="J36" s="5" t="n"/>
@@ -3317,9 +3308,7 @@
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>McGurk effect: https://en.wikipedia.org/wiki/McGurk_effect
-Olfactory memory (koku-anı): https://en.wikipedia.org/wiki/Olfactory_memory
-Placebo (Harvard Health): https://www.health.harvard.edu/mental-health/the-power-of-the-placebo-effect</t>
+          <t>McGurk effect: https://en.wikipedia.org/wiki/McGurk_effect Olfactory memory (koku-anı): https://en.wikipedia.org/wiki/Olfactory_memory Placebo (Harvard Health): https://www.health.harvard.edu/mental-health/the-power-of-the-placebo-effect</t>
         </is>
       </c>
       <c r="J37" s="5" t="n"/>
@@ -3387,7 +3376,7 @@
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
-          <t>YÜKLENDİ (https://youtu.be/c0lcGGWy-hw)</t>
+          <t>Wikipedia — Blind spot (vision): https://en.wikipedia.org/wiki/Blind_spot_(vision)</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -4453,8 +4442,7 @@
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>NOAA Ocean Exploration — Bioluminescence: https://oceanexplorer.noaa.gov/facts/bioluminescence.html
-Smithsonian Ocean — Bioluminescence: https://ocean.si.edu/ocean-life/fish/bioluminescence</t>
+          <t>NOAA Ocean Exploration — Bioluminescence: https://oceanexplorer.noaa.gov/facts/bioluminescence.html Smithsonian Ocean — Bioluminescence: https://ocean.si.edu/ocean-life/fish/bioluminescence</t>
         </is>
       </c>
       <c r="J53" s="5" t="n"/>
@@ -5292,7 +5280,7 @@
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>Kaynak: Wikipedia / MarineBio — Sea Otter Tool Use &amp; Fur Density</t>
+          <t>Wikipedia / MarineBio — Sea Otter Tool Use &amp; Fur Density: https://en.wikipedia.org/wiki/Sea_otter</t>
         </is>
       </c>
       <c r="J65" s="5" t="n"/>
@@ -6552,7 +6540,7 @@
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>Journal of Voice / Auditory Bone Conduction</t>
+          <t>Journal of Voice / Wikipedia — Auditory Bone Conduction: https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
       <c r="J83" s="5" t="n"/>
@@ -6694,7 +6682,7 @@
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>PLOS ONE (2012) — Vailati et al. / Journal of Experimental Biology</t>
+          <t>PLOS ONE (2012) — Vailati et al. (Archerfish Water Jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
         </is>
       </c>
       <c r="J85" s="5" t="n"/>
@@ -6765,7 +6753,7 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>IEEE Electromagnetic Shielding / Faraday Cage</t>
+          <t>IEEE Electromagnetic Shielding / Wikipedia — Faraday Cage: https://en.wikipedia.org/wiki/Faraday_cage</t>
         </is>
       </c>
       <c r="J86" s="5" t="n"/>
@@ -6836,7 +6824,7 @@
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>NASA Heliophysics / SOHO Solar Acoustics</t>
+          <t>NASA Heliophysics / SOHO — Solar Acoustics: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
         </is>
       </c>
       <c r="J87" s="5" t="n"/>
@@ -6907,7 +6895,7 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Texas A&amp;M College of Medicine / Autonomic Sneezing Reflex</t>
+          <t>Texas A&amp;M College of Medicine / Wikipedia — Photic &amp; Autonomic Sneezing Reflex: https://en.wikipedia.org/wiki/Sneeze</t>
         </is>
       </c>
       <c r="J88" s="5" t="n"/>
@@ -6978,7 +6966,7 @@
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>Journal of Archaeological Science (2012) — Lipo &amp; Hunt</t>
+          <t>Journal of Archaeological Science (2012) — Lipo &amp; Hunt (Easter Island Moai): https://en.wikipedia.org/wiki/Moai</t>
         </is>
       </c>
       <c r="J89" s="5" t="n"/>
@@ -7049,7 +7037,7 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>Nature Communications (2019) — de Santana et al.</t>
+          <t>Nature Communications (2019) — de Santana et al. (860V Electric Eel): https://www.nature.com/articles/s41467-019-11622-9</t>
         </is>
       </c>
       <c r="J90" s="5" t="n"/>
@@ -7120,7 +7108,7 @@
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>ASME A17.1 Escalator Safety Code</t>
+          <t>ASME A17.1 Escalator Safety Code — Escalator Skirt Deflector Brushes: https://en.wikipedia.org/wiki/Escalator</t>
         </is>
       </c>
       <c r="J91" s="5" t="n"/>
@@ -7191,7 +7179,7 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>Nature Astronomy — Diamond Rain on Ice Giants</t>
+          <t>Nature Astronomy / SLAC — Diamond Rain on Ice Giants: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7230,7 @@
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>ESA FOTON-M3 Tardigrade Mission</t>
+          <t>ESA FOTON-M3 / Current Biology — Tardigrades in Space: https://en.wikipedia.org/wiki/Tardigrade</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7281,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>Hess &amp; Polt — Pupillometry Research</t>
+          <t>Hess &amp; Polt (1960) / Wikipedia — Pupillometry Research: https://en.wikipedia.org/wiki/Pupillometry</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7332,7 @@
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>US Forest Service — Pando Clonal Colony</t>
+          <t>USDA Forest Service — Pando Clonal Colony: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7383,7 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>NOAA Severe Weather — Return Stroke Physics</t>
+          <t>NOAA Severe Weather — Lightning Return Stroke Physics: https://www.weather.gov/safety/lightning-science</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7434,7 @@
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>NASA Juno Mission — Great Red Spot</t>
+          <t>NASA Juno Mission — Jupiter Great Red Spot: https://science.nasa.gov/jupiter/facts/</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7485,7 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>NASA Mars Exploration — Olympus Mons</t>
+          <t>NASA Mars Exploration — Olympus Mons: https://science.nasa.gov/mars/facts/</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7536,7 @@
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>Smithsonian Ocean — Sea Stars Anatomy</t>
+          <t>Smithsonian Ocean / Wikipedia — Sea Stars Anatomy: https://en.wikipedia.org/wiki/Starfish</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7587,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>Neuroscience Reviews — Unihemispheric Sleep</t>
+          <t>Sleep Foundation / Wikipedia — Unihemispheric Slow-Wave Sleep: https://en.wikipedia.org/wiki/Unihemispheric_slow-wave_sleep</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7638,7 @@
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>NASA Cassini Mission — Saturn Planetary Density</t>
+          <t>NASA Cassini Mission — Saturn Planetary Density: https://science.nasa.gov/saturn/facts/</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7689,7 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>PLOS Biology — Human Microbiome Cell Count</t>
+          <t>PLOS Biology (Sender et al., 2016) — Revised Estimates for Human &amp; Bacteria Cells: https://journals.plos.org/plosbiology/article?id=10.1371/journal.pbio.1002533</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7740,7 @@
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
-          <t>American Journal of Physics — Cathedral Glass</t>
+          <t>American Journal of Physics (Zanotto, 1998) — Do Cathedral Glasses Flow?: https://en.wikipedia.org/wiki/Glass</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7791,7 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>NASA Lunar Laser Ranging Experiment</t>
+          <t>NASA — Lunar Laser Ranging Experiment: https://science.nasa.gov/moon/facts/</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7842,7 @@
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
-          <t>Cornell Feline Health Center — Cat Vocalization</t>
+          <t>Cornell Feline Health Center / Wikipedia — Cat Vocalization: https://en.wikipedia.org/wiki/Cat_communication</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7893,7 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>NASA Earth Fact Sheet — Orbital Velocity</t>
+          <t>NASA Earth Fact Sheet — Orbital Velocity: https://science.nasa.gov/earth/facts/</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7944,7 @@
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
-          <t>Smithsonian — Honey's Eternal Shelf Life</t>
+          <t>Smithsonian Magazine — The Science Behind Honey's Eternal Shelf Life: https://en.wikipedia.org/wiki/Honey</t>
         </is>
       </c>
     </row>
@@ -8007,7 +7995,7 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>Science — Earth's Inner Core Temperature</t>
+          <t>Science / Wikipedia — Earth's Inner Core Temperature: https://en.wikipedia.org/wiki/Earth%27s_inner_core</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8046,7 @@
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>Stanford University — Elephant Seismic Hearing</t>
+          <t>Stanford University / Wikipedia — Elephant Seismic Communication: https://en.wikipedia.org/wiki/Elephant_cognition</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8097,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>NASA Uranus Planetary Fact Sheet</t>
+          <t>NASA — Uranus Planetary Fact Sheet: https://science.nasa.gov/uranus/facts/</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8148,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Nature Reviews Neuroscience — 10% Brain Myth</t>
+          <t>Nature Reviews Neuroscience — The 10% Brain Myth: https://en.wikipedia.org/wiki/Ten_percent_of_brain_myth</t>
         </is>
       </c>
     </row>
@@ -8248,9 +8236,9 @@
       <c r="D113" s="14" t="inlineStr">
         <is>
           <t>Şu an başını kaldırıp gökyüzüne baktığında, Güneş'in hâlâ orada olduğundan gerçekten emin misin? Ya tam şu saniye sessizce söndüyse? İşin en ürpertici kısmı ne biliyor musun? Bunu tam sekiz dakika yirmi saniye boyunca ruhun bile duymayacak. Çünkü Güneş'ten çıkan son ışık gözüne ulaşana kadar gökyüzü masmavi kalır. Ama sekizinci dakikanın sonunda gökyüzü bir anda zifiri karanlığa gömülür ve Dünya yörüngeden kopup buzlu boşluğa savrulur. Peki sen o son sekiz dakikayı dışarıda gökyüzünü izleyerek mi geçirirdin, yoksa yeraltı sığınaklarına inerek mi? Yorumlarda buluşalım.
-Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Sunlight
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: NASA / Wikipedia — Sunlight (Işık Hızı ve Güneş Işığı Süresi): https://en.wikipedia.org/wiki/Sunlight
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8276,7 +8264,7 @@
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Sunlight</t>
+          <t>NASA / Wikipedia — Sunlight (Işık Hızı ve Güneş Işığı Süresi): https://en.wikipedia.org/wiki/Sunlight</t>
         </is>
       </c>
     </row>
@@ -8299,9 +8287,9 @@
       <c r="D114" s="14" t="inlineStr">
         <is>
           <t>Gece gökyüzüne baktığında, Ay'ın hep aynı yerde durduğunu sanıyorsun değil mi? Peki ya Ay Dünya'ya doğru yaklaşmaya başlasaydı ne olurdu? İlk başta gökyüzünde devasa görünürdü ama hemen ardından kütle çekim kabusu başlardı. Okyanuslar yüzlerce metre yükselip kıyı şehirlerini yutardı. Dünya'ya on sekiz bin kilometre mesafedeki Roche sınırına girdiği anda ise Ay gökyüzünde paramparça olur ve Dünya'nın etrafında tıpkı Satürn gibi parlak bir halka oluştururdu. Peki sen gökyüzünde Satürn gibi dev bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım.
-Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Roche_limit
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: NASA / Wikipedia — Roche Limit (Gelgit Parçalanma Sınırı): https://en.wikipedia.org/wiki/Roche_limit
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8327,7 +8315,7 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Roche_limit</t>
+          <t>NASA / Wikipedia — Roche Limit (Gelgit Parçalanma Sınırı): https://en.wikipedia.org/wiki/Roche_limit</t>
         </is>
       </c>
     </row>
@@ -8350,9 +8338,9 @@
       <c r="D115" s="14" t="inlineStr">
         <is>
           <t>Uzayda tek başına süzülürken bir anda ağlamaya başlasan gözyaşlarının yanağından aşağı süzüleceğini mi sanıyorsun? Hiç de öyle olmaz. Dünya'da gözyaşını aşağı çeken şey yerçekimidir. Ama uzayın ağırlıksız boşluğunda, su moleküllerini birbirine kenetleyen yüzey gerilimi tek patron haline gelir. Gözünden çıkan her damla, akmak yerine göz pınarının tam üzerinde şeffaf, titreyen bir su küresine dönüşür ve sen bir bezle silene kadar yüzünden asla ayrılmaz. Peki sen yerçekimsiz ortamda yaşamayı deneyimlemek mi isterdin, yoksa ayağının yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım.
-Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Surface_tension
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: CSA / Wikipedia — Surface Tension in Microgravity (Uzayda Yüzey Gerilimi): https://en.wikipedia.org/wiki/Surface_tension
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8378,7 +8366,7 @@
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Surface_tension</t>
+          <t>CSA / Wikipedia — Surface Tension in Microgravity (Uzayda Yüzey Gerilimi): https://en.wikipedia.org/wiki/Surface_tension</t>
         </is>
       </c>
     </row>
@@ -8401,9 +8389,9 @@
       <c r="D116" s="14" t="inlineStr">
         <is>
           <t>Gündüz vakti masmavi gökyüzünde bir anda ikinci bir Güneş'in parladığını hayal et. Dünya'ya elli ışık yılı mesafede dev bir yıldız süpernova olarak patlasaydı tam olarak bunu yaşardık. Haftalarca geceleri bile gökyüzü hiç kararmazdı. Ama asıl tehlike o parlak ışık değil, görünmez gama ışınları olurdu. Üst atmosferdeki ozon tabakası hızla erir ve yüzeye inen radyasyon okyanuslardaki besin zincirini altüst ederdi. Peki böyle bir kozmik patlama görsen, önce teleskopla izlemeye mi koşardın yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım.
-Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Near-Earth_supernova
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
+📚 Kaynak: NASA / Wikipedia — Near-Earth Supernova (Yakın Süpernova Etkileri): https://en.wikipedia.org/wiki/Near-Earth_supernova
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8429,7 +8417,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
+          <t>NASA / Wikipedia — Near-Earth Supernova (Yakın Süpernova Etkileri): https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
         </is>
       </c>
     </row>
@@ -8452,9 +8440,9 @@
       <c r="D117" s="14" t="inlineStr">
         <is>
           <t>Elindeki küçücük bir çay kaşığının Everest Dağı kadar ağır olabileceğini hayal edebilir misin? Evrenin en ekstrem canavarı olan nötron yıldızlarıyla tanış. Dev bir yıldız çöktüğünde çekirdeği o kadar korkunç sıkışır ki, koca bir Güneş sadece yirmi kilometre çapında bir küreye hapsolur. Bu yıldızdan alacağın tek bir çay kaşığı madde tam bir milyar ton ağırlığındadır. Onu Dünya'da elinden bıraksan toprağı ve kayaları delip doğrudan gezegenin çekirdeğine kadar batardı. Peki seni uzayda en çok büyüleyen şey, kara delikler mi yoksa nötron yıldızları mı? Yorumlarda buluşalım.
-Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Neutron_star
-🎨 Görseller temsilîdir (AI üretimi ve NASA/ESO uzay arşivi).
+💬 Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: NASA / Wikipedia — Neutron Star (Nötron Yıldızı Yoğunluğu): https://en.wikipedia.org/wiki/Neutron_star
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
@@ -8480,7 +8468,7 @@
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Neutron_star</t>
+          <t>NASA / Wikipedia — Neutron Star (Nötron Yıldızı Yoğunluğu): https://en.wikipedia.org/wiki/Neutron_star</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8491,10 @@
       <c r="D118" s="14" t="inlineStr">
         <is>
           <t>Bir ses kaydında kendi sesini duyduğun an “Bu gerçekten benim sesim mi?” diye yüzünü buruşturduğun oldu mu? Merak etme, yalnız değilsin. Sen konuşurken sesini iki farklı yoldan aynı anda duyarsın. Hem havadan kulağına gelen dalgalarla, hem de ses tellerinin kafatası kemiklerini titreştirerek iç kulağına gönderdiği kemik iletimiyle. Kafatası kemiklerin bas frekansları güçlendirdiği için kendi sesini hep daha tok ve derin algılarsın. Ama kayıtta, kemik iletimi devreden çıkar ve başkalarının duyduğu o gerçek sesine yüzleşirsin. Peki sen kayıtlarda kendi sesini dinlemeye alışabildin mi, yoksa duyunca hemen kapatıyor musun? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/Bone_conduction</t>
+💬 Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇
+📚 Kaynak: Journal of Voice / Wikipedia — Bone Conduction (Kafatası Kemik İletimi): https://en.wikipedia.org/wiki/Bone_conduction
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -8528,7 +8519,7 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Bone_conduction</t>
+          <t>Journal of Voice / Wikipedia — Bone Conduction (Kafatası Kemik İletimi): https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8542,10 @@
       <c r="D119" s="14" t="inlineStr">
         <is>
           <t>Yüksek bir balkonun ya da uçurumun kenarından aşağı baktığında içinde hiçbir kötü niyet yokken bile bir anda “Ya şimdi atlarsam” diye ürpertici bir düşünce geçti mi? Fransızların “boşluğun çağrısı” dediği bu durum aslında beyninin aşırı hızlı çalışan bir hayatta kalma alarmıdır. Beynin kenara yaklaştığında denge merkezine “Geri çekil, tehlikedesin” sinyali gönderir. Bilinçli zihnin ise bu ani geri çekilme refleksini sanki aşağı atlamak istemişim de kendimi zor tutmuşum gibi yanlış yorumlar. Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
+💬 Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım! 👇
+📚 Kaynak: Journal of Affective Disorders / Wikipedia — High Place Phenomenon (Boşluğun Çağrısı): https://en.wikipedia.org/wiki/The_imp_of_the_perverse
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
@@ -8576,7 +8570,7 @@
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
+          <t>Journal of Affective Disorders / Wikipedia — High Place Phenomenon (Boşluğun Çağrısı): https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8593,10 @@
       <c r="D120" s="14" t="inlineStr">
         <is>
           <t>Çok acı bir biber ısırdığında ağzının alev alev yandığını hissediyorsun ya, sana dilinin aslında hiç yanmadığını, tamamen beyninin kandırıldığını söylesem? Biberin içindeki kapsaisin molekülü dokularına fiziksel bir zarar vermez. Sadece dilindeki 43 derecenin üzerindeki sıcaklıklarda açılan ısı alıcılarına gizlice kilitlenir ve beynine ağzın kaynar suyla yanıyor diye sahte bir alarm gönderir. Üstelik kapsaisin suda çözünmediği için su içmek yangını ağzının her yerine yayar. Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa ayrana koşmak mı? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/Capsaicin</t>
+💬 Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa yoğurt ve ayrana koşmak mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: Nature (Caterina et al.) / Wikipedia — Capsaicin &amp; TRPV1 Receptor: https://en.wikipedia.org/wiki/Capsaicin
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
@@ -8624,7 +8621,7 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Capsaicin</t>
+          <t>Nature (Caterina et al.) / Wikipedia — Capsaicin &amp; TRPV1 Receptor: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8644,10 @@
       <c r="D121" s="14" t="inlineStr">
         <is>
           <t>Dondurucu bir soğukta dışarı çıktığında, ne kadar sıkmaya çalışırsan çalış, dişlerinin kendi kendine takırdadığı oldu mu? Bunu durduramazsın. Çünkü o an kontrol beynindeki hipotalamus adlı gizli termostata geçer. İç sıcaklığın milimetrik olarak düştüğü anda, beynin kaslarını saniyede defalarca kasılıp gevşemeye zorlayarak acil ısı üretir. Çene kasların vücudunun en güçlü ve beynine en yakın kas grubu olduğu için bu titreme en şiddetli orada hissedilir ve dişlerin birbirine vurur. Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/Shivering</t>
+💬 Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa kavurucu yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: NIH / Wikipedia — Shivering &amp; Hypothalamic Thermoregulation (İrade Dışı Titreme): https://en.wikipedia.org/wiki/Shivering
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Shivering</t>
+          <t>NIH / Wikipedia — Shivering &amp; Hypothalamic Thermoregulation (İrade Dışı Titreme): https://en.wikipedia.org/wiki/Shivering</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,10 @@
       <c r="D122" s="14" t="inlineStr">
         <is>
           <t>Herkesin içinde bir anda utandığında neden kolların değil de sadece yanakların ve kulakların alev alev kızarır? Üstelik sakın kızarma dedikçe daha da kıpkırmızı olursun. Charles Darwin'in tüm duyguların en insaniye olanı dediği bu tepki vücudunun gizli dürüstlük mekanizmasıdır. Utandığın saniye beynin ani bir adrenalin salgılar ve sadece yüzündeki özel kılcal damarlar genişleyerek cildinin altına sıcak kan hücum eder. Evrimsel olarak bu tek kelime etmeden çevrendekilere hata yaptım ve farkındayım demenin sessiz yoludur. Peki sen utandığında sakin kalabilenlerden misin, yoksa saniyesinde kızaranlardan mı? Yorumlarda buluşalım.
-Kaynak: https://en.wikipedia.org/wiki/Blushing</t>
+💬 Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: Charles Darwin / Wikipedia — Blushing Physiology (Yüz Kızarması Mekanizması): https://en.wikipedia.org/wiki/Blushing
+🎨 Görseller temsilîdir (AI üretimi).
+#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -8720,7 +8723,7 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Blushing</t>
+          <t>Charles Darwin / Wikipedia — Blushing Physiology (Yüz Kızarması Mekanizması): https://en.wikipedia.org/wiki/Blushing</t>
         </is>
       </c>
     </row>
@@ -8743,8 +8746,9 @@
       <c r="D123" s="14" t="inlineStr">
         <is>
           <t>Dünya üzerinde öyle ıssız bir nokta var ki, orada bir tekneyle mahsur kalsan sana en yakın insanlar Dünya'da değil, uzayda olurdu. Güney Pasifik Okyanusu'nun ortasındaki Point Nemo ile tanış. Burası en yakın kara parçasına tam 2.688 kilometre uzaklıktadır. Buna karşılık, Uluslararası Uzay İstasyonu başının sadece 400 kilometre üzerinden geçer. Yani gökyüzündeki astronotlar, sana karadaki insanlardan tam 6 kat daha yakındır. Uzay ajansları da ömrü biten uyduları bu dev su mezarlığına düşürür. Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Pole_of_inaccessibility
+💬 Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇
+📚 Kaynak: NOAA / Wikipedia — Oceanic Pole of Inaccessibility (Point Nemo): https://en.wikipedia.org/wiki/Pole_of_inaccessibility
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
         </is>
       </c>
@@ -8770,7 +8774,7 @@
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
+          <t>NOAA / Wikipedia — Oceanic Pole of Inaccessibility (Point Nemo): https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
         </is>
       </c>
     </row>
@@ -8793,8 +8797,9 @@
       <c r="D124" s="14" t="inlineStr">
         <is>
           <t>Antarktika'nın bembeyaz, dondurucu buzullarının arasından bir anda kıpkırmızı, kan renginde bir şelalenin aktığını görsen ne düşünürdün? Taylor Buzulu'ndaki bu ürpertici manzaranın sebebi kan ya da yosun değil, tam 5 milyon yıl önce buzulun 400 metre altına hapsolmuş antik bir yeraltı gölü. Bu gizli gölün suyu okyanuslardan 3 kat daha tuzlu olduğu için dondurucu soğukta bile asla donmuyor. İçindeki yoğun demir, buzulun çatlaklarından sızıp milyonlarca yıl sonra ilk kez havadaki oksijenle temas ettiği anda saniyeler içinde paslanarak kıpkırmızı bir şelaleye dönüşüyor. Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Blood_Falls
+💬 Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇
+📚 Kaynak: NSF / Wikipedia — Blood Falls, Taylor Glacier Antarctica (Kan Şelalesi): https://en.wikipedia.org/wiki/Blood_Falls
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
         </is>
       </c>
@@ -8820,7 +8825,7 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Blood_Falls</t>
+          <t>NSF / Wikipedia — Blood Falls, Taylor Glacier Antarctica (Kan Şelalesi): https://en.wikipedia.org/wiki/Blood_Falls</t>
         </is>
       </c>
     </row>
@@ -8843,8 +8848,9 @@
       <c r="D125" s="14" t="inlineStr">
         <is>
           <t>Tam 5,5 milyon yıl boyunca güneş ışığının tek bir zerresini bile görmemiş, mühürlü bir yeraltı dünyasının kapısını açtığını hayal et. Romanya'da tesadüfen keşfedilen Movile Mağarası, dış dünyadan tamamen kopuk bambaşka bir gezegen gibi. İçerideki havada oksijen normalin yarısından bile az, atmosferi ise zehirli hidrojen sülfür ve karbondioksitle dolu. Güneş ışığı olmadığı için buradaki yaşam tamamen kimyasal enerjiyle ayakta kalıyor ve içeride gözleri yok olmuş, sadece buraya özgü 30'dan fazla gizemli canlı türü yaşıyor. Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Movile_Cave
+💬 Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇
+📚 Kaynak: BBC / Wikipedia — Movile Cave Chemosynthesis Ecosystem (Movile Mağarası): https://en.wikipedia.org/wiki/Movile_Cave
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
         </is>
       </c>
@@ -8870,7 +8876,7 @@
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Movile_Cave</t>
+          <t>BBC / Wikipedia — Movile Cave Chemosynthesis Ecosystem (Movile Mağarası): https://en.wikipedia.org/wiki/Movile_Cave</t>
         </is>
       </c>
     </row>
@@ -8893,8 +8899,9 @@
       <c r="D126" s="14" t="inlineStr">
         <is>
           <t>Şu gördüğün neon sarısı ve zümrüt yeşili göller başka bir gezegene değil, Dünya üzerindeki en tehlikeli cehenneme ait. Etiyopya'daki Danakil Çöküntüsü'nde yer alan Dallol Volkanı, deniz seviyesinin 48 metre altında kaynayan dev bir kimya laboratuvarı gibidir. Yerin altındaki kızgın magma, kalın tuz ve kükürt yataklarıyla buluştuğunda, yüzeye akü asidinden bile daha yakıcı kaynar sular ve zehirli klor gazları fışkırır. Burada maskesiz uzun süre nefes almak bile imkânsızdır. Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)
+💬 Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Nature Ecology &amp; Evolution / Wikipedia — Dallol Hydrothermal System: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
         </is>
       </c>
@@ -8920,7 +8927,7 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
+          <t>Nature Ecology &amp; Evolution / Wikipedia — Dallol Hydrothermal System: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
         </is>
       </c>
     </row>
@@ -8943,8 +8950,9 @@
       <c r="D127" s="14" t="inlineStr">
         <is>
           <t>Yerin tam 2.224 metre altına, yani üst üste dizilmiş 7 Eyfel Kulesi derinliğine karanlık bir kuyudan indiğini hayal et. Kafkas Dağları'ndaki Krubera Mağarası, Dünya'nın bilinen en derin uçurumlarından biridir. Buraya inen mağaracıların en dibe ulaşması haftalar sürer ve içeride yeraltı şelaleleriyle buz gibi su tünelleri vardır. En şaşırtıcı olanı ise, 2.000 metre derinlikteki o dondurucu ve ışıksız sularda bile dış dünyayı hiç görmemiş şeffaf canlıların yaşamaya devam etmesidir. Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım!
-Daha fazla bilgi dozu için takip etmeyi unutma! 🔔
-Kaynak: https://en.wikipedia.org/wiki/Krubera_Cave
+💬 Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: National Geographic / Wikipedia — Krubera Cave (Dünya'nın En Derin Mağaraları): https://en.wikipedia.org/wiki/Krubera_Cave
+🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
         </is>
       </c>
@@ -8970,7 +8978,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Krubera_Cave</t>
+          <t>National Geographic / Wikipedia — Krubera Cave (Dünya'nın En Derin Mağaraları): https://en.wikipedia.org/wiki/Krubera_Cave</t>
         </is>
       </c>
     </row>
@@ -8993,8 +9001,8 @@
       <c r="D128" s="14" t="inlineStr">
         <is>
           <t>Denizin dibinde iki bin yıl boyunca paslanmış bir Yunan batığından, modern saatler kadar karmaşık dişlilere sahip antik bir bilgisayar çıktığını biliyor muydun?
-Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Antikythera_mechanism
+💬 Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Nature / Wikipedia — Antikythera Mechanism (2.100 Yıllık Antik Analog Bilgisayar): https://en.wikipedia.org/wiki/Antikythera_mechanism
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9021,7 +9029,7 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
+          <t>Nature / Wikipedia — Antikythera Mechanism (2.100 Yıllık Antik Analog Bilgisayar): https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
         </is>
       </c>
     </row>
@@ -9044,8 +9052,8 @@
       <c r="D129" s="14" t="inlineStr">
         <is>
           <t>Kapadokya'nın altında, yirmi bin insanın hayvanları ve erzaklarıyla birlikte haftalarca hiç yeryüzüne çıkmadan yaşayabildiği sekiz katlı dev bir yeraltı şehri var: Derinkuyu.
-Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Derinkuyu_underground_city
+💬 Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
+📚 Kaynak: UNESCO / Wikipedia — Derinkuyu Underground City (Derinkuyu Yeraltı Şehri): https://en.wikipedia.org/wiki/Derinkuyu_underground_city
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9072,7 +9080,7 @@
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
+          <t>UNESCO / Wikipedia — Derinkuyu Underground City (Derinkuyu Yeraltı Şehri): https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
         </is>
       </c>
     </row>
@@ -9095,8 +9103,8 @@
       <c r="D130" s="14" t="inlineStr">
         <is>
           <t>Dünyanın en iyi şifre çözücüleri, dilbilimcileri ve yapay zekâları bir araya geldi ama altı yüz yıllık bu kitabın tek bir cümlesini bile okuyamadı: Voynich El Yazması.
-Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Voynich_manuscript
+💬 Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Yale Beinecke Library / Wikipedia — Voynich Manuscript (Voynich El Yazması): https://en.wikipedia.org/wiki/Voynich_manuscript
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9123,7 +9131,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Voynich_manuscript</t>
+          <t>Yale Beinecke Library / Wikipedia — Voynich Manuscript (Voynich El Yazması): https://en.wikipedia.org/wiki/Voynich_manuscript</t>
         </is>
       </c>
     </row>
@@ -9146,8 +9154,8 @@
       <c r="D131" s="14" t="inlineStr">
         <is>
           <t>Deniz seviyesinden üç bin sekiz yüz metre yüksekte, aralarına jilet bile girmeyecek kadar kusursuz kesilmiş yüz tonluk taş bloklar düşün: Puma Punku.
-Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Pumapunku
+💬 Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
+📚 Kaynak: UNESCO / Wikipedia — Pumapunku Andesite Megaliths (Puma Punku H-Blokları): https://en.wikipedia.org/wiki/Pumapunku
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9174,7 +9182,7 @@
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Pumapunku</t>
+          <t>UNESCO / Wikipedia — Pumapunku Andesite Megaliths (Puma Punku H-Blokları): https://en.wikipedia.org/wiki/Pumapunku</t>
         </is>
       </c>
     </row>
@@ -9197,8 +9205,8 @@
       <c r="D132" s="14" t="inlineStr">
         <is>
           <t>Dünyanın Yedi Harikası'ndan biri sayılan Babil'in Asma Bahçeleri'nin aslında hiçbir zaman Babil'de olmadığını duysan ne derdin?
-Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
-📚 Kaynak: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon
+💬 Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Oxford University (Stephanie Dalley) / Wikipedia — Hanging Gardens of Babylon: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon
 🎨 Görseller temsilîdir (AI üretimi).
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
@@ -9225,7 +9233,7 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
+          <t>Oxford University (Stephanie Dalley) / Wikipedia — Hanging Gardens of Babylon: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
         </is>
       </c>
     </row>
@@ -9282,9 +9290,9 @@
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Bone_conduction
-https://en.wikipedia.org/wiki/The_imp_of_the_perverse
-https://en.wikipedia.org/wiki/Capsaicin</t>
+          <t>1) Kemik İletimi — Wikipedia: https://en.wikipedia.org/wiki/Bone_conduction
+2) Boşluğun Çağrısı — Wikipedia: https://en.wikipedia.org/wiki/The_imp_of_the_perverse
+3) Kapsaisin &amp; TRPV1 — Wikipedia: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
     </row>

--- a/baslik.xlsx
+++ b/baslik.xlsx
@@ -3021,56 +3021,64 @@
       <c r="M41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>YÜKLENMEDİ</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>YÜKLENDİ</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>video_35.mp4</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Vücudundaki Tüm Acıyı Yöneten Beynin Kendisi Acı Hissedemez! 🧠⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Elimiz yandığında ya da dizimiz çarptığında acıyı bize hissettiren merkez beyindir; ancak beyin dokusunun kendisinde tek bir ağrı alıcısı (nosiseptör) bile yoktur! Baş ağrısı dediğimiz şey aslında beynin kendisinden değil, onu saran zarlar ve kan damarlarındaki gerilimden kaynaklanır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #bilim</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>bilgidozu, beyin, ağrı, nörobilim, anatomi, insanvücudu, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Beyin dokusunun hiç acı hissetmediğini biliyor muydun? 🧠⚡ Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>BrainFacts (Society for Neuroscience): https://www.brainfacts.org/</t>
         </is>
       </c>
-      <c r="J42" s="6" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" s="7" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>https://youtu.be/da3y0_DfWYQ</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24 18:22</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -8107,7 +8115,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 17:55</t>
+          <t>2026-10-24 18:22</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -8116,11 +8124,11 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>video_34.mp4 yayınlandı (https://youtu.be/tCuQNw_V74I) · Sıradaki: video_35.mp4</t>
+          <t>video_35.mp4 yayınlandı (https://youtu.be/da3y0_DfWYQ) · Sıradaki: video_36.mp4</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8464,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Sıradaki Shorts: video_35.mp4 · Sıradaki Uzun Video: uzun_video_8.mp4 yayın saatini bekliyor.</t>
+          <t>Sıradaki Shorts: video_36.mp4 · Sıradaki Uzun Video: uzun_video_8.mp4 yayın saatini bekliyor.</t>
         </is>
       </c>
     </row>

--- a/baslik.xlsx
+++ b/baslik.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8100,6 +8100,56 @@
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="5" t="n"/>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>video_131.mp4</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Kâğıt Kesiği Neden Bu Kadar Acıtır? 🩹 #bilgidozu #shorts</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Küçücük bir kâğıt kesiği neden beklediğinden çok daha fazla can yakar? Parmak uçlarımız dokunma ve ağrıyı algılayan yoğun duyu sinirleriyle donatılmıştır. Üstelik çıplak gözle düz görünen kâğıt kenarı, mikroskobik ölçekte lifli ve düzensiz bir yapıya sahiptir; gün boyu ellerimizi kullanmaya devam etmemiz de hassaslaşan dokuyu tekrar tekrar uyarır.
+Senin de başına geldi mi? Yorumlarda buluşalım! 👇
+📚 Kaynak: Dr. Hayley Goldbach (UCLA Dermatology) / BBC Future &amp; StatPearls
+🎨 Görseller temsilîdir (AI bilimsel canlandırma).</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #insanvücudu #beyin #bilim</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>bilgi dozu, kağıt kesiği, insan vücudu, duyu sinirleri, bilim, ilginç bilgiler, shorts</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Senin de başına geldi mi? En son ne zaman kâğıt kesiği yaşadın, yorumlara yaz! 👇</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>İnsan Vücudu ve Beyin</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>BBC Future (Dr. H. Goldbach, UCLA, 2016) &amp; StatPearls</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/baslik.xlsx
+++ b/baslik.xlsx
@@ -62,7 +62,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +87,12 @@
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -101,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -120,6 +126,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3382,178 +3397,178 @@
       <c r="M48" s="3" t="n"/>
     </row>
     <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>video_47.mp4</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>Mide Asidi Bu Kadar Güçlüyken Miden Kendi Kendini Neden Sindirmez? 🧬🔥 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Mide asidin yediğin en sert besinleri bile parçalayacak kadar güçlüdür; peki miden kendi kendini neden sindirmez? Midenin iç duvarını kaplayan hücreler sürekli olarak bikarbonat bakımından zengin kalın bir mukus tabakası salgılar ve yüzey hücreleri birkaç günde bir yenilenerek asidin dokuya zarar vermesini engeller.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #vücut #bilim</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, mide, mideasidi, insanvücudu, biyoloji, anatomi, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>Midenin iç yüzeyinin birkaç günde bir tamamen yenilendiğini biliyor muydun? 🧬🔥 Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>Wikipedia — Gastric mucosal barrier: https://en.wikipedia.org/wiki/Gastric_mucosal_barrier</t>
         </is>
       </c>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>video_52.mp4</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Vücudunda Kanla Değil, Doğrudan Havadan Nefes Alan Tek Doku! 👁️🌬️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Gözünün en dışındaki şeffaf kornea tabakasında tek bir kan damarı bile yoktur ve oksijenini doğrudan havadan alır! Işığın göze engelsiz girmesi için kornea tamamen cam gibi saydam kalmak zorundadır; bu yüzden kan damarları yerine gözyaşı filminde çözünen atmosfer oksijeniyle doğrudan nefes alır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #vücut #bilim</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, göz, kornea, insanvücudu, biyoloji, anatomi, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Gözümüzün kornea tabakasının doğrudan havadan oksijen aldığını biliyor muydun? 👁️🌬️ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>Wikipedia — Cornea Physiology: https://en.wikipedia.org/wiki/Cornea</t>
         </is>
       </c>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="5" t="n"/>
-      <c r="M50" s="5" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="8" t="n"/>
     </row>
     <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>video_57.mp4</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>Bacak Kasların Yorulurken Kalbin Neden Hayat Boyu Hiç Yorulmaz? ❤️⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Koşarken bacak kasların dakikalar içinde yorulup yanarken kalbinin hayat boyu hiç durmadan atıp yorulmamasının sırrı hücre yapısındadır! İskelet kaslarında enerji üreten mitokondriler hücre hacminin yalnızca küçük bir kısmını kaplarken, kalp kası hücrelerinin yaklaşık %40'ı mitokondrilerle doludur ve her atışta enerjisini anında yeniler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #vücut #bilim</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, kalp, mitokondri, insanvücudu, biyoloji, anatomi, ilginçbilgiler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Kalp kası hücrelerinin %40'ının enerji santrali mitokondrilerden oluştuğunu biliyor muydun? ❤️⚡ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>NIH PMC / Wikipedia — Cardiac muscle: https://en.wikipedia.org/wiki/Cardiac_muscle</t>
         </is>
       </c>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>video_62.mp4</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Suda Kalan Parmaklarımız Su Çektiği İçin Buruşmuyor! İşte Gerçek Sebebi! 🖐️💧 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Suda fazla kaldığında parmak uçlarının suyu sünger gibi çektiği için buruştuğunu sanıyorsan yanılıyorsun! Beynin yönettiği bu otonom sinir sistemi refleksinin sırrını inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -3562,53 +3577,53 @@
 #bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, suda parmak buruşması, sinir sistemi, insan vücudu, biyoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🖐️💧</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Brain, Behavior and Evolution / Newcastle University: https://en.wikipedia.org/wiki/Wrinkle#Water-immersion_wrinkling</t>
         </is>
       </c>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
-      <c r="L52" s="5" t="n"/>
-      <c r="M52" s="5" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="8" t="n"/>
     </row>
     <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>video_67.mp4</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu Karanlıkta Gerçekten Işık Saçıyor Ama Gözümüz Göremiyor! ✨🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>İnsan vücudunun karanlıkta tıpkı ateş böcekleri gibi gerçekten ışık saçtığını ama gözlerimizin bunu göremediğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -3617,53 +3632,53 @@
 #bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, insan biyolüminesansı, insan vücudu ışık saçıyor, biyoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ✨🧠</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>PLOS ONE (2009) — Kobayashi et al.: https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0006256</t>
         </is>
       </c>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="8" t="n"/>
     </row>
     <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>video_72.mp4</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>Ses Kaydındaki Sesin Sana Neden Bambaşka Geliyor? 🎙️🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Ses kaydını dinlediğinde kendi sesinin sana neden bambaşka ve tuhaf geldiğini biliyor muydun? Kafatası kemik iletimi ile hava iletimi arasındaki farkı inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -3672,53 +3687,53 @@
 #bilgidozu #shorts #psikoloji #beyin #bilim</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #psikoloji #beyin #bilim</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, ses kaydı, kendi sesimiz, kemik iletimi, beyin, psikoloji, insan vücudu, shorts</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🎙️🧠</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>Journal of Voice / Wikipedia — Auditory Bone Conduction: https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="8" t="n"/>
     </row>
     <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>video_77.mp4</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>Gözlerin Açıkken Hapşırmak Neden İmkansız? Beynin O Salisede Ne Yapar? 🤧👁️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>Gözlerin açıkken hapşırmanın neden neredeyse imkansız olduğunu ve beyninin o salisede neden göz kapaklarını kilitlediğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -3727,53 +3742,53 @@
 #bilgidozu #shorts #insanvücudu #refleks #bilim</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #refleks #bilim</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, hapşırma refleksi, göz açık hapşırmak, insan vücudu, beyin, bilim, shorts</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🤧👁️</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>Biyoloji ve Vücut</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>Texas A&amp;M College of Medicine / Wikipedia — Photic &amp; Autonomic Sneezing Reflex: https://en.wikipedia.org/wiki/Sneeze</t>
         </is>
       </c>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="8" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>video_106.mp4</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Kendi Sesini Kayıtta Dinleyince Neden Tuhaf Gelir? 🎙️🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Bir ses kaydında kendi sesini duyduğun an “Bu gerçekten benim sesim mi?” diye yüzünü buruşturduğun oldu mu? Merak etme, yalnız değilsin. Sen konuşurken sesini iki farklı yoldan aynı anda duyarsın. Hem havadan kulağına gelen dalgalarla, hem de ses tellerinin kafatası kemiklerini titreştirerek iç kulağına gönderdiği kemik iletimiyle. Kafatası kemiklerin bas frekansları güçlendirdiği için kendi sesini hep daha tok ve derin algılarsın. Ama kayıtta, kemik iletimi devreden çıkar ve başkalarının duyduğu o gerçek sesine yüzleşirsin. Peki sen kayıtlarda kendi sesini dinlemeye alışabildin mi, yoksa duyunca hemen kapatıyor musun? Yorumlarda buluşalım.
 💬 Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇
@@ -3782,53 +3797,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Peki sen kendi sesini kayıtlarda dinlemeye alışabildin mi, yoksa duyunca hâlâ hemen kapatıyor musun? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>Journal of Voice / Wikipedia — Bone Conduction (Kafatası Kemik İletimi): https://en.wikipedia.org/wiki/Bone_conduction</t>
         </is>
       </c>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="8" t="n"/>
     </row>
     <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>video_107.mp4</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>Yüksek Bir Yerden Bakınca Beyin Neden 'Atla' Diye Fısıldar? 🧗‍♂️🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Yüksek bir balkonun ya da uçurumun kenarından aşağı baktığında içinde hiçbir kötü niyet yokken bile bir anda “Ya şimdi atlarsam” diye ürpertici bir düşünce geçti mi? Fransızların “boşluğun çağrısı” dediği bu durum aslında beyninin aşırı hızlı çalışan bir hayatta kalma alarmıdır. Beynin kenara yaklaştığında denge merkezine “Geri çekil, tehlikedesin” sinyali gönderir. Bilinçli zihnin ise bu ani geri çekilme refleksini sanki aşağı atlamak istemişim de kendimi zor tutmuşum gibi yanlış yorumlar. Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım.
 💬 Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım! 👇
@@ -3837,53 +3852,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Peki sen yüksek bir yerden aşağı baktığında o ürpertiyi hissediyor musun, yoksa yüksekten hiç etkilenmeyenlerden misin? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>Journal of Affective Disorders / Wikipedia — High Place Phenomenon (Boşluğun Çağrısı): https://en.wikipedia.org/wiki/The_imp_of_the_perverse</t>
         </is>
       </c>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="8" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>video_108.mp4</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Acı Biber Aslında Ağzını Yakmaz — Beynini Nasıl Kandırır? 🌶️🔥 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Çok acı bir biber ısırdığında ağzının alev alev yandığını hissediyorsun ya, sana dilinin aslında hiç yanmadığını, tamamen beyninin kandırıldığını söylesem? Biberin içindeki kapsaisin molekülü dokularına fiziksel bir zarar vermez. Sadece dilindeki 43 derecenin üzerindeki sıcaklıklarda açılan ısı alıcılarına gizlice kilitlenir ve beynine ağzın kaynar suyla yanıyor diye sahte bir alarm gönderir. Üstelik kapsaisin suda çözünmediği için su içmek yangını ağzının her yerine yayar. Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa ayrana koşmak mı? Yorumlarda buluşalım.
 💬 Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa yoğurt ve ayrana koşmak mı? Yorumlarda buluşalım! 👇
@@ -3892,53 +3907,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Peki acı yediğinde senin ilk refleksin soğuk suya sarılmak mı oluyor, yoksa yoğurt ve ayrana koşmak mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>Nature (Caterina et al.) / Wikipedia — Capsaicin &amp; TRPV1 Receptor: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="8" t="n"/>
+      <c r="M58" s="8" t="n"/>
     </row>
     <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>video_109.mp4</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>Soğukta Dişlerin Neden İrade Dışı Takırdar? 🥶🦷 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Dondurucu bir soğukta dışarı çıktığında, ne kadar sıkmaya çalışırsan çalış, dişlerinin kendi kendine takırdadığı oldu mu? Bunu durduramazsın. Çünkü o an kontrol beynindeki hipotalamus adlı gizli termostata geçer. İç sıcaklığın milimetrik olarak düştüğü anda, beynin kaslarını saniyede defalarca kasılıp gevşemeye zorlayarak acil ısı üretir. Çene kasların vücudunun en güçlü ve beynine en yakın kas grubu olduğu için bu titreme en şiddetli orada hissedilir ve dişlerin birbirine vurur. Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım.
 💬 Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa kavurucu yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım! 👇
@@ -3947,53 +3962,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>Peki sen dondurucu kış soğuğuna daha kolay dayananlardan mısın, yoksa kavurucu yaz sıcağını tercih edenlerden mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>NIH / Wikipedia — Shivering &amp; Hypothalamic Thermoregulation (İrade Dışı Titreme): https://en.wikipedia.org/wiki/Shivering</t>
         </is>
       </c>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="n"/>
-      <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="8" t="n"/>
+      <c r="M59" s="8" t="n"/>
     </row>
     <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>video_110.mp4</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>Utandığında Neden Sadece Yüzün ve Kulakların Kızarır? 😳🧠 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Herkesin içinde bir anda utandığında neden kolların değil de sadece yanakların ve kulakların alev alev kızarır? Üstelik sakın kızarma dedikçe daha da kıpkırmızı olursun. Charles Darwin'in tüm duyguların en insaniye olanı dediği bu tepki vücudunun gizli dürüstlük mekanizmasıdır. Utandığın saniye beynin ani bir adrenalin salgılar ve sadece yüzündeki özel kılcal damarlar genişleyerek cildinin altına sıcak kan hücum eder. Evrimsel olarak bu tek kelime etmeden çevrendekilere hata yaptım ve farkındayım demenin sessiz yoludur. Peki sen utandığında sakin kalabilenlerden misin, yoksa saniyesinde kızaranlardan mı? Yorumlarda buluşalım.
 💬 Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇
@@ -4002,53 +4017,53 @@
 #bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #nörobilim #insanbedeni #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, shorts, nörobilim, insan bedeni, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Peki sen utandığında rengini belli etmeden sakin kalabilenlerden misin, yoksa saniyesinde pancar gibi kızaranlardan mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>Nörobilim ve İnsan Bedeni</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>Charles Darwin / Wikipedia — Blushing Physiology (Yüz Kızarması Mekanizması): https://en.wikipedia.org/wiki/Blushing</t>
         </is>
       </c>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+      <c r="L60" s="8" t="n"/>
+      <c r="M60" s="8" t="n"/>
     </row>
     <row r="61" ht="42" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>video_91.mp4</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>Vücudundaki Hücrelerin Yarısından Fazlası Aslında Bakteri! 🦠🧬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>İnsan bedeninde yaklaşık 30 trilyon insan hücresine karşılık 38 trilyondan fazla dost bakteri hücresi yaşar.
 Peki vücudunuzda kendi hücrelerinizden daha fazla bakteri yaşaması size nasıl hissettiriyor? Yorumlara yazın! 👇
@@ -4057,53 +4072,53 @@
 #bilgidozu #shorts #insanvücudu #bilim #biyoloji</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #bilim #biyoloji</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, insan vücudu, bakteri, biyoloji, bilim, shorts</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Peki vücudunuzda kendi hücrelerinizden daha fazla bakteri yaşaması size nasıl hissettiriyor? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>PLOS Biology (Sender et al., 2016) — Revised Estimates for Human &amp; Bacteria Cells: https://journals.plos.org/plosbiology/article?id=10.1371/journal.pbio.1002533</t>
         </is>
       </c>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="8" t="n"/>
+      <c r="M61" s="8" t="n"/>
     </row>
     <row r="62" ht="42" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>video_100.mp4</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Beynimizin Sadece Yüzde 10'unu Kullandığımız Efsanesi Yalan! 🧠⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Modern beyin görüntüleme cihazları gün içinde konuşurken, yürürken ve uyurken beynimizin neredeyse tamamının aktif çalıştığını kanıtlamıştır.
 Siz de yıllarca beynimizin sadece yüzde onunu kullandığımız efsanesine inanmış mıydınız? Yorumlara yazın! 👇
@@ -4112,53 +4127,53 @@
 #bilgidozu #shorts #beyin #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, beyin, yüzde 10 efsanesi, psikoloji, nörobilim, shorts</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Siz de yıllarca beynimizin sadece yüzde onunu kullandığımız efsanesine inanmış mıydınız? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>Nature Reviews Neuroscience — The 10% Brain Myth: https://en.wikipedia.org/wiki/Ten_percent_of_brain_myth</t>
         </is>
       </c>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
+      <c r="M62" s="8" t="n"/>
     </row>
     <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>video_121.mp4</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Rüyanda Neden Koşamazsın? Beynin Gece Seni Kilitler! 🧠</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Rüyanda tehlikeden kaçmaya çalışırken bacaklarının kurşun gibi ağırlaştığını hiç hissettin mi? REM uykusu sırasında beynin uyanıkmış gibi aktif çalışır ancak beyin sapındaki devreler GABA ve glisin aracılığıyla iskelet kaslarına giden motor nöronları geçici olarak kilitler. REM atonisi denilen bu koruyucu mekanizma sayesinde rüyalarını yatakta fiziksel olarak oynamaz ve kendine zarar vermezsin.
 Peki sen rüyanda daha çok koşamadığın mı yoksa bağıramadığın anları mı yaşıyorsun? Yorumlarda buluşalım! 👇
@@ -4167,53 +4182,53 @@
 #bilgidozu #shorts #beyin #uyku #psikoloji #nörobilim #bilim</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #beyin #uyku #psikoloji #nörobilim #bilim</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, rüyanda neden koşamazsın, rem uykusu, uyku atonisi, beyin, nörobilim, psikoloji, uyku bilimi, ilginç bilgiler, şaşırtıcı gerçekler, bilim, shorts</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Peki sen rüyanda daha çok koşamadığın mı yoksa bağıramadığın anları mı yaşıyorsun? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>https://www.jneurosci.org/content/32/29/9785</t>
         </is>
       </c>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="5" t="n"/>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+      <c r="L63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
     </row>
     <row r="64" ht="42" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>video_83.mp4</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Sevdiğin Birine Bakınca Göz Bebeğin Neden Otomatik Büyür? 👀❤️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Hoşlandığımız birine baktığımızda dopamin ve oksitosin etkisiyle sempatik sinir sistemi göz bebeklerimizi istemsizce büyütür.
 Siz konuşurken karşınızdakinin göz bebeklerine dikkat eder misiniz? Yorumlara yazın! 👇
@@ -4222,53 +4237,53 @@
 #bilgidozu #shorts #psikoloji #insanvücudu #bilim</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #psikoloji #insanvücudu #bilim</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, psikoloji, göz bebeği, insan vücudu, bilim, shorts</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Siz konuşurken karşınızdakinin göz bebeklerine dikkat eder misiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Psikoloji</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>Hess &amp; Polt (1960) / Wikipedia — Pupillometry Research: https://en.wikipedia.org/wiki/Pupillometry</t>
         </is>
       </c>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n"/>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+      <c r="L64" s="8" t="n"/>
+      <c r="M64" s="8" t="n"/>
     </row>
     <row r="65" ht="42" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>uzun_video_8.mp4</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Okyanusta Kendi Işığını Üreten Canlılar: Soğuk Işık, Av Tuzağı ve Karşı Aydınlatma! 🌊✨ #bilgidozu</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>Güneş ışığının ulaşamadığı derin okyanus sularında kendi ışığını üreten canlıların kimyasal sırrı ne? Denizlerin alacakaranlık kuşağında parlayan biyolüminesans dünyasını inceliyoruz! 🌊✨
 BÖLÜMLER:
@@ -4280,53 +4295,53 @@
 #bilgidozu #okyanus #bilim #biyolüminesans #doğa #denizcanlıları</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, okyanus, biyolüminesans, derin deniz, fenerbalığı, doğa, biyoloji, bilim, ilginç bilgiler</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Derin okyanustaki hangi ışık stratejisi seni en çok şaşırttı? 🌊 1-Soğuk Işık 2-Fener Tuzağı 3-Görünmezlik — Yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>Uzun — Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>NOAA Ocean Exploration — Bioluminescence: https://oceanexplorer.noaa.gov/facts/bioluminescence.html Smithsonian Ocean — Bioluminescence: https://ocean.si.edu/ocean-life/fish/bioluminescence</t>
         </is>
       </c>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="n"/>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
+      <c r="L65" s="8" t="n"/>
+      <c r="M65" s="8" t="n"/>
     </row>
     <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>uzun_video_9.mp4</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Beynin Seni Ayakta Tutan 3 Gizli Sensörü: İç Kulak Pusulası, Kristaller ve Algı Çatışması! 🧠⚡ #bilgidozu</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Yürürken başını çevirdiğinde görüntü neden titremiyor? Araçta telefon okurken neden miden bulanıyor? Vücudumuzun görünmez denge merkezi olan vestibüler sistemi inceliyoruz! 🧠⚡
 BÖLÜMLER:
@@ -4338,53 +4353,53 @@
 #bilgidozu #beyin #nörobilim #denge #psikoloji #bilim</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, beyin, nörobilim, denge, içkulak, vestibülersistem, algı, psikoloji, bilim</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Arabada veya gemide giderken telefon okuyabiliyor musun, yoksa hemen miden mi bulanıyor? 🚗🧠 Yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>Uzun — Beyin ve Psikoloji</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>NIH / NIDCD — Balance Disorders: https://www.nidcd.nih.gov/health/balance-disorders</t>
         </is>
       </c>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
     </row>
     <row r="67" ht="42" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>uzun_video_10.mp4</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>Uzay Sessizse NASA'nın Kaydettiği Bu Sesler Ne? Kara Delik Seslerinin Gerçek Sırrı! 🪐🔊 #bilgidozu</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>Uzay boşluğunda ses yayılmıyorsa NASA'nın paylaştığı kara delik ve galaksi sesleri gerçekte ne? Perseus galaksi kümesindeki gerçek basınç dalgaları ile M87 veri sonifikasyonunun farkını inceliyoruz! 🪐🔊
 BÖLÜMLER:
@@ -4396,53 +4411,53 @@
 #bilgidozu #uzay #nasa #karadelik #astronomi #bilim</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, nasa, karadelik, perseus, m87, chandra, astronomi, astrofizik, bilim</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Perseus kara deliğinin 57 oktav yükseltilmiş gerçek basınç sesini duymuş muydun? 🕳️🔊 Duyanlar 1, yeni öğrenenler 2 yazsın! 👇</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Uzun — Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" s="8" t="inlineStr">
         <is>
           <t>NASA — New NASA Black Hole Sonifications: https://www.nasa.gov/universe/new-nasa-black-hole-sonifications-with-a-remix/</t>
         </is>
       </c>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="n"/>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+      <c r="L67" s="8" t="n"/>
+      <c r="M67" s="8" t="n"/>
     </row>
     <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>uzun_video_11.mp4</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>Zaman Yukarıda Daha Hızlı Akıyor! Telefonundaki Konum İçin Einstein Neden Gerekli? ⏱️🛰️ #bilgidozu</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Telefonundaki mavi konum noktasının doğru çalışması için Einstein'ın özel ve genel görelilik kuramlarının her saniye hesaba katıldığını biliyor muydun? ⏱️🛰️
 BÖLÜMLER:
@@ -4454,53 +4469,53 @@
 #bilgidozu #uzay #zaman #einstein #görelilik #bilim</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, uzay, zaman, einstein, görelilik, atomsaati, gps, fizik, bilim</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Einstein'ın görelilik hesabı olmasa GPS konumunun günde 10 kilometre sapacağını biliyor muydun? ⏱️🛰️ 1 veya 2 yaz! 👇</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>Uzun — Fizik ve Uzay</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>NIST — Putting Einstein to the Test: https://www.nist.gov/atomic-clocks/a-powerful-tool-for-science/putting-einstein-test</t>
         </is>
       </c>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="8" t="n"/>
+      <c r="M68" s="8" t="n"/>
     </row>
     <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>uzun_video_12.mp4</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>Sizin Beğendikleriniz · Bölüm 1: Kargalar, Ahtapotlar, Tardigradlar! 🐙🔬 #bilgidozu</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>Sizin Beğendikleriniz serisinin ilk bölümünde üç efsane canlının sıra dışı biyolojisini inceliyoruz: kargaların yüz hafızası ve sosyal öğrenmesi, ahtapotların kollara dağılmış sinir sistemi ile üç kalbi ve tardigradların kriptobiyoz dayanıklılığı.
 BÖLÜMLER:
@@ -4518,27 +4533,27 @@
 #bilgidozu #bilim #doğa #hayvanlar #biyoloji</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim #doğa #hayvanlar #biyoloji</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, kargalar, ahtapot, tardigrad, su ayısı, hayvanlar, doğa, bilim, biyoloji, ilginç bilgiler</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Bu 3 olaydan sizi en çok hangisi şaşırttı: 1 mi, 2 mi, 3 mü? Yorumlara yazın! (1 Kargalar, 2 Ahtapotlar, 3 Tardigradlar)</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>Uzun — Bilim ve Doğa</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>Kargalar — Marzluff et al. (2012), PNAS: https://www.pnas.org/doi/10.1073/pnas.1206109109
 Kargalar sosyal öğrenme — Cornell et al. (2011), Proc. R. Soc. B: https://doi.org/10.1098/rspb.2011.0957
@@ -4548,28 +4563,28 @@
 Tardigrad Dsup — Hashimoto et al. (2016), Nature Communications: https://www.nature.com/articles/ncomms12808</t>
         </is>
       </c>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
     </row>
     <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>uzun_video_13.mp4</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>Beyninin Senden Gizlediği 3 Otomatik Hile (Kendi Sesin, Boşluğun Çağrısı ve Sahte Acı) 🧠🔒 #bilgidozu</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Beyninin senden gizlediği 3 otomatik hileyi tek bir merak yolculuğunda inceliyoruz:
 1 · Kendi Sesin Neden Kayıtta Yabancı Gelir? (Kafatası Kemik İletimi)
@@ -4584,37 +4599,37 @@
 #bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #bilim #psikoloji #nörobilim #insanbedeni</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, nörobilim, psikoloji, insan beyni, kemik iletimi, kapsaisin, bilim, belgesel</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Bu 3 beyin hilesinden seni en çok şaşırtan hangisi oldu: Kendi sesinin kemik iletimi mi, yüksek yerdeki Boşluğun Çağrısı mı, yoksa acı biberin sahte yanık alarmı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>Uzun — Nörobilim ve Psikoloji</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>1) Kemik İletimi — Wikipedia: https://en.wikipedia.org/wiki/Bone_conduction
 2) Boşluğun Çağrısı — Wikipedia: https://en.wikipedia.org/wiki/The_imp_of_the_perverse
 3) Kapsaisin &amp; TRPV1 — Wikipedia: https://en.wikipedia.org/wiki/Capsaicin</t>
         </is>
       </c>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+      <c r="L70" s="8" t="n"/>
+      <c r="M70" s="8" t="n"/>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -4677,490 +4692,490 @@
       <c r="M71" s="3" t="n"/>
     </row>
     <row r="72" ht="42" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>video_41.mp4</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Eşini Etkilemek İçin Renkli Karnını Açıp Dans Eden Minik Örümcek! 🕷️💃 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Avustralya'da yaşayan ve pirinç tanesi kadar küçük olan tavuskuşu örümceği, doğanın en renkli dansçılarından biridir! Erkek örümcekler gökkuşağı renklerindeki karın kanatlarını yelpaze gibi açar, üçüncü bacaklarını havaya kaldırır ve çıkardıkları titreşimlerle kusursuz bir ritim sergiler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, tavuskuşuörümceği, doğa, hayvanlaralemi, biyoloji, avustralya, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Örümceklerden korkanları bile gülümsetecek bir dans değil mi? 🕷️💃 Beğenenler '1' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>Western Australian Museum — Peacock Spider: https://museum.wa.gov.au/explore/articles/peacock-spiders</t>
         </is>
       </c>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="n"/>
-      <c r="L72" s="5" t="n"/>
-      <c r="M72" s="5" t="n"/>
+      <c r="J72" s="8" t="n"/>
+      <c r="K72" s="8" t="n"/>
+      <c r="L72" s="8" t="n"/>
+      <c r="M72" s="8" t="n"/>
     </row>
     <row r="73" ht="42" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>video_42.mp4</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Doğada Havada Asılı Kalıp Geriye Doğru Uçabilen Tek Kuş! 🐦🔄 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Sinek kuşları, kuşlar dünyasında uzun süreli olarak geriye doğru uçabilen tek türdür! Kanatlarını sadece aşağı-yukarı değil, omuz eklemlerinden sekiz çizecek şekilde döndürerek saniyede 50 ila 80 kez çırparlar; böylece helikopter gibi havada sabit kalıp geri vitese takabilirler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, sinekkuşu, kuşlar, doğa, biyoloji, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Sinek kuşunun saniyede 80 kez kanat çırptığını biliyor muydun? 🐦🔄 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>UC Davis — Hummingbird Facts: https://www.ucdavis.edu/</t>
         </is>
       </c>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="n"/>
-      <c r="L73" s="5" t="n"/>
-      <c r="M73" s="5" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="8" t="n"/>
+      <c r="M73" s="8" t="n"/>
     </row>
     <row r="74" ht="42" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>video_43.mp4</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Suyun Altından Ağaçtaki Böceği Su Tabancası Gibi Vuran Balık! 🐟🎯 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Okçu balığı, suyun dışındaki dallarda duran böcekleri ağzından fırlattığı keskin bir su jetiyle vurarak avlar! Üstelik ışığın sudan havaya geçerken kırılmasını (optik kırılmayı) doğuştan hesaba katar ve hedefine neredeyse sıfır hatayla nişan alır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, okçubalığı, balıklar, doğa, fizik, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Işığın kırılmasını hesaplayıp suyla ateş eden bu keskin nişancı balığı duymuş muydun? 🐟🎯 '1' veya '2' yaz! 👇</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>PLOS ONE (Vailati et al., 2012 — Archerfish water jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
         </is>
       </c>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
-      <c r="L74" s="5" t="n"/>
-      <c r="M74" s="5" t="n"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
+      <c r="L74" s="8" t="n"/>
+      <c r="M74" s="8" t="n"/>
     </row>
     <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>video_44.mp4</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>Sadece Rengini Değil, Derisinin Dokusunu da Anında Değiştiren Canlı! 🦑🎭 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Mürekkep balığı, okyanusun en üstün kamuflaj ustalarından biridir! Derisindeki milyonlarca renk hücresiyle saniyede renk ve desen değiştirirken, özel kas kabarcıkları (papilla) sayesinde pürüzsüz derisini anında dikenli bir mercan ya da pütürlü bir kaya dokusuna dönüştürebilir.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, mürekkepbalığı, okyanus, kamuflaj, doğa, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>Mürekkep balığının derisini 3 boyutlu olarak kabartıp kaya şekline sokabildiğini biliyor muydun? 🦑🎭 '1' / '2' yaz! 👇</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>Marine Biological Laboratory — Cuttlefish Camouflage: https://www.mbl.edu/</t>
         </is>
       </c>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="5" t="n"/>
-      <c r="L75" s="5" t="n"/>
-      <c r="M75" s="5" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="8" t="n"/>
+      <c r="M75" s="8" t="n"/>
     </row>
     <row r="76" ht="42" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>video_45.mp4</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Flamingolar Aslında Gri Doğar! Peki Tüyleri Neden Pembeleşir? 🦩🦐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Flamingolar dünyaya geldiklerinde pembe değil, gri ve beyaz tüylere sahiptir! İkonik pembe ve mercan renklerini, sulak alanlarda tükettikleri mikroskobik algler ve tuzlu su karideslerinin içindeki 'karotenoid' pigmentlerinin karaciğerde işlenip yeni çıkan tüylere yerleşmesiyle kazanırlar.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, flamingo, kuşlar, doğa, biyoloji, hayvanlaralemi, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>Flamingoların gri doğduğunu ve yedikleriyle pembeleştiğini biliyor muydun? 🦩🦐 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>San Diego Zoo — Flamingo Facts: https://animals.sandiegozoo.org/animals/flamingo</t>
         </is>
       </c>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="n"/>
-      <c r="L76" s="5" t="n"/>
-      <c r="M76" s="5" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="8" t="n"/>
+      <c r="M76" s="8" t="n"/>
     </row>
     <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>video_49.mp4</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Bu Hayvanın Parmak İzi İnsanla O Kadar Aynı ki Mikroskopta Bile Karışıyor! 🐨🔍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Bir koalanın parmak izi insanınkine o kadar kusursuz benzer ki taramalı elektron mikroskobu altında bile ayırt etmek oldukça zordur! Evrimsel olarak bizden milyonlarca yıl önce ayrılmış olsalar da okaliptüs dallarını sıkıca kavrama ihtiyacı, koalalarda insanla neredeyse birebir aynı parmak izi kıvrımlarını oluşturmuştur.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, koala, parmakizi, doğa, hayvanlaralemi, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>Koalaların parmak izinin insanla neredeyse birebir aynı olduğunu biliyor muydun? 🐨🔍 Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>Wikipedia — Koala (Fingerprints): https://en.wikipedia.org/wiki/Koala</t>
         </is>
       </c>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="n"/>
-      <c r="L77" s="5" t="n"/>
-      <c r="M77" s="5" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
     </row>
     <row r="78" ht="42" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>video_50.mp4</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga Fırın Yemeği İçeriden Dışarıya Doğru Pişirmez! İşte Gerçek! ⚡🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga fırının yemeği içeriden dışarıya doğru pişirdiği bilgisi tamamen bir şehir efsanesidir! Mikrodalgalar besinin dış yüzeyinden içeriye yalnızca birkaç santimetre nüfuz ederek su moleküllerini titreştirir; kalın yiyeceklerin en iç kısmı ise dış katmandan içeriye yayılan normal ısı iletimiyle ısınır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, mikrodalga, fizik, teknoloji, günlükhayat, efsaneavrı, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>Mikrodalganın yemeği içeriden dışarıya pişirdiğini sananlardan mıydın? ⚡🔬 Evet diyenler '1', gerçeği bilenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Bilim</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>FDA — Microwave Oven Radiation: https://www.fda.gov/radiation-emitting-products/resources-you-radiation-emitting-products/microwave-oven-radiation</t>
         </is>
       </c>
-      <c r="J78" s="5" t="n"/>
-      <c r="K78" s="5" t="n"/>
-      <c r="L78" s="5" t="n"/>
-      <c r="M78" s="5" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
+      <c r="L78" s="8" t="n"/>
+      <c r="M78" s="8" t="n"/>
     </row>
     <row r="79" ht="42" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>video_51.mp4</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>Uzay Boşluk Olmasaydı Güneş'in Devasa Uğultusunu Dünya'dan Duyardık! ☀️🔊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>Uzay boşluk olmasaydı, Güneş'in devasa uğultusunu Dünya'dan sürekli duyardık! Güneş yüzeyinin altındaki kaynayan dev plazma hücreleri sürekli yükselip çökerken muazzam ses dalgaları üretir; aradaki 150 milyon kilometrelik vakum sesi iletmediği için Dünya sessizdir, aksi halde gökyüzü kesintisiz bir motor gürültüsüyle çınlardı.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, güneş, uzay, ses, astronomi, fizik, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>Uzayda hava olsaydı Güneş'in uğultusunu 150 milyon km öteden duyacağımızı biliyor muydun? ☀️🔊 Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>ESA SOHO — Solar Interior Helioseismology: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
         </is>
       </c>
-      <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="n"/>
-      <c r="L79" s="5" t="n"/>
-      <c r="M79" s="5" t="n"/>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="8" t="n"/>
+      <c r="L79" s="8" t="n"/>
+      <c r="M79" s="8" t="n"/>
     </row>
     <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>video_53.mp4</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Tutankhamun'un Mezarındaki Hançer Uzaydan Gelen Göktaşından Yapılmış! 🗡️☄️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Mısır Firavunu Tutankhamun'un mezarında bulunan ünlü demir hançerin Dünya dışından gelen bir göktaşından dövüldüğü kanıtlandı! X-ışını analizleri, demir çağı başlamadan asırlar önce yapılan bu bıçakta yüksek oranda nikel ve kobalt bulunduğunu, yani firavunun hançerinin gerçekten uzaydan düşen bir meteoritten üretildiğini ortaya koydu.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, tutankhamun, mısır, göktaşı, tarih, arkeoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>Tutankhamun'un hançerinin uzaydan düşen bir göktaşından yapıldığını biliyor muydun? 🗡️☄️ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>Wikipedia — Tutankhamun's meteoric iron dagger: https://en.wikipedia.org/wiki/Tutankhamun%27s_meteoric_iron_dagger</t>
         </is>
       </c>
-      <c r="J80" s="5" t="n"/>
-      <c r="K80" s="5" t="n"/>
-      <c r="L80" s="5" t="n"/>
-      <c r="M80" s="5" t="n"/>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
+      <c r="L80" s="8" t="n"/>
+      <c r="M80" s="8" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>video_54.mp4</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Koltuk Altındaki Gizli Cebinde Kendi Çekiç Taşını Taşıyan Hayvan! 🦦🪨 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Deniz samurlarının koltuk altlarında gizli bir deri cebi olduğunu ve burada en sevdikleri taşı sakladıklarını biliyor muydun? Çoğu deniz memelisinin aksine kalın bir yağ tabakası olmayan bu canlılar, santimetrekarede 150.000 teli bulan dünyanın en yoğun kürküyle ısınır. Sol koltuk altlarındaki gevşek deri kesesini ise avladıkları kabukluları ve kendi çekiç taşlarını taşımak için kullanırlar.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 👇
@@ -5170,313 +5185,313 @@
 #bilgidozu #shorts #doğa #hayvanlar #denizsamuru #bilim #ilginçbilgiler</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, shorts, deniz samuru, su samuru, koltuk altı cebi, alet kullanan hayvanlar, doğa ve hayvanlar, ilginç bilgiler, bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa, doz dışı</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>Deniz samurlarının koltuk altında kendi çekiç taşını taşıdığını daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🦦🪨👇</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>Wikipedia / MarineBio — Sea Otter Tool Use &amp; Fur Density: https://en.wikipedia.org/wiki/Sea_otter</t>
         </is>
       </c>
-      <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="n"/>
-      <c r="L81" s="5" t="n"/>
-      <c r="M81" s="5" t="n"/>
+      <c r="J81" s="8" t="n"/>
+      <c r="K81" s="8" t="n"/>
+      <c r="L81" s="8" t="n"/>
+      <c r="M81" s="8" t="n"/>
     </row>
     <row r="82" ht="42" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>video_55.mp4</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>Uçak Pencerelerinin Altındaki O Minik Delik Neden Var? ✈️🪟 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Uçak pencerelerinin alt kısmındaki o minik delik bir üretim hatası değil, hayat kurtaran bir mühendislik detayıdır! Üç ayrı akrilik katmandan oluşan uçak pencerelerinin ortadaki camında yer alan bu nefes deliği, yüksek irtifadaki dev basınç yükünü en dıştaki kalın cama aktarır ve camların buğulanıp buz tutmasını önler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, uçak, havacılık, mühendislik, fizik, günlükhayat, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>Uçak camındaki o minik deliğin ne işe yaradığını daha önce merak etmiş miydin? ✈️🪟 Bilenler '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>Business Insider / FAA — Airplane Window Bleed Hole: https://www.businessinsider.com/airplane-windows-tiny-holes-2016-3</t>
         </is>
       </c>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n"/>
-      <c r="L82" s="5" t="n"/>
-      <c r="M82" s="5" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
+      <c r="L82" s="8" t="n"/>
+      <c r="M82" s="8" t="n"/>
     </row>
     <row r="83" ht="42" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>video_56.mp4</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>Bir Kibrit Kutusu Kadar Parçası 3 Milyar Ton Çeken Yıldız! 🪐⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>Uzayda yalnızca bir kibrit kutusu büyüklüğündeki parçası Dünya'da tam 3 milyar ton ağırlığında çeken nötron yıldızları vardır! Dev bir yıldız süpernova olarak çöküp patladığında Güneş'ten fazla kütle 20 kilometre çapındaki bir küreye sıkışır ve atomların içindeki boşluk yok olarak bir kibrit kutusu madde 800 metrelik bir kaya dağı kadar ağırlaşır.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, nötronyıldızı, uzay, astronomi, astrofizik, evren, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>Bir kibrit kutusu nötron yıldızı maddesinin Dünya'da 3 milyar ton çektiğini biliyor muydun? 🪐⚡ Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Neutron Star: https://en.wikipedia.org/wiki/Neutron_star</t>
         </is>
       </c>
-      <c r="J83" s="5" t="n"/>
-      <c r="K83" s="5" t="n"/>
-      <c r="L83" s="5" t="n"/>
-      <c r="M83" s="5" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
+      <c r="L83" s="8" t="n"/>
+      <c r="M83" s="8" t="n"/>
     </row>
     <row r="84" ht="42" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>video_58.mp4</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Vezüv Patlamasında Beyni Gerçek Siyah Cama Dönüşen Romalı! 🌋🖤 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>MS 79 yılındaki Vezüv Yanardağı patlamasında Herculaneum kentinde hayatını kaybeden genç bir Romalının beyninin aşırı sıcaklıktan gerçek siyah cama dönüştüğü kanıtlandı! 510 derecelik kavurucu kül bulutuyla saniyeler içinde ısınan ve hemen ardından hızla soğuyan beyin dokusu, nöron yapılarını bile koruyarak obsidyen benzeri cama dönüştü.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, vezüv, herculaneum, pompeii, tarih, arkeoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>Vezüv patlamasında 510 derecelik kül bulutuyla bir insanın beyninin siyah cama dönüştüğünü biliyor muydun? 🌋🖤 Duyanlar '1', şaşıranlar '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>BBC / Scientific Reports — Herculaneum Glass Brain: https://www.bbc.com/news/articles/cgr2n8xx5gyo</t>
         </is>
       </c>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="n"/>
-      <c r="L84" s="5" t="n"/>
-      <c r="M84" s="5" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
+      <c r="L84" s="8" t="n"/>
+      <c r="M84" s="8" t="n"/>
     </row>
     <row r="85" ht="42" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>video_59.mp4</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Bu Hayvan Su Altında Nefesini Yunuslardan 4 Kat Uzun Tutuyor! 🦥🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>Karada dünyanın en yavaş memelisi olan tembel hayvanlar, su altında nefesini yunuslardan bile 4 kat daha uzun tutabilir! Yunuslar yaklaşık 10 dakikada bir yüzeye çıkarken, tembel hayvanlar suya girdiklerinde kalp atış hızlarını normalin üçte birine düşürüp metabolizmalarını yavaşlatarak tam 40 dakika boyunca nefes almadan kalabilir.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, tembelhayvan, yunus, doğa, hayvanlaralemi, biyoloji, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>Tembel hayvanların su altında nefesini 40 dakika tutarak yunusları bile geçtiğini biliyor muydun? 🦥🌊 Duyanlar '1', ilk kez öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>BBC Bitesize — Sloths Hold Breath 40 Minutes: https://www.bbc.co.uk/bitesize/articles/zqk4qyc</t>
         </is>
       </c>
-      <c r="J85" s="5" t="n"/>
-      <c r="K85" s="5" t="n"/>
-      <c r="L85" s="5" t="n"/>
-      <c r="M85" s="5" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
+      <c r="L85" s="8" t="n"/>
+      <c r="M85" s="8" t="n"/>
     </row>
     <row r="86" ht="42" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>video_60.mp4</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Araba Ön Camlarındaki Siyah Noktalar Neden Var? Süs Değilmiş! 🚗⚫ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Araba ön camlarının kenarındaki siyah şerit (frit bandı) ve küçülerek dağılan siyah noktalar süs değil, kritik bir mühendislik kalkanıdır! Cama fırınlanan bu seramik katman, camı gövdeye bağlayan yapıştırıcıyı güneşin morötesi ışınlarından korurken, siyah noktalar cam yüksek ısıda bükülürken sıcaklığı eşit dağıtarak optik bozulmayı önler.
 Daha fazla bilgi dozu için takip etmeyi unutma!</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, araba, otomobil, mühendislik, fizik, günlükhayat, ilginçbilgiler, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Araba camlarının kenarındaki siyah noktaların yapıştırıcıyı güneşten koruduğunu biliyor muydun? 🚗⚫ Duyanlar '1', yeni öğrenenler '2' yazsın! 👇</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Jalopnik / Pilkington — Windshield Frit Dots: https://www.jalopnik.com/heres-what-those-little-dots-are-on-the-edges-of-your-c-1791075995/</t>
         </is>
       </c>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
-      <c r="L86" s="5" t="n"/>
-      <c r="M86" s="5" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
+      <c r="L86" s="8" t="n"/>
+      <c r="M86" s="8" t="n"/>
     </row>
     <row r="87" ht="42" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>video_61.mp4</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>Tepesinden Atlayınca Dibe Düşmenin 12 Dakika Sürdüğü 20 Km'lik Uçurum! 🪐🧗 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Tepesinden atladığında yere çarpmanın tam 12 dakika sürdüğü devasa bir uçurum olduğunu biliyor muydun? Uranüs'ün uydusu Miranda üzerindeki 20 km'lik Verona Rupes uçurumunu inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5485,53 +5500,53 @@
 #bilgidozu #shorts #uzay #miranda #bilim</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #miranda #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, verona rupes, miranda, uranüs, uzay, astronomi, uçurum, nasa, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🧗</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
         <is>
           <t>NASA Voyager 2 / USGS Astrogeology — Verona Rupes: https://en.wikipedia.org/wiki/Verona_Rupes</t>
         </is>
       </c>
-      <c r="J87" s="5" t="n"/>
-      <c r="K87" s="5" t="n"/>
-      <c r="L87" s="5" t="n"/>
-      <c r="M87" s="5" t="n"/>
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
+      <c r="L87" s="8" t="n"/>
+      <c r="M87" s="8" t="n"/>
     </row>
     <row r="88" ht="42" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>video_63.mp4</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>Harç ve Çimento Olmadan Depremde Yıkılmayan 500 Yıllık İnka Duvarları! 🏛️🪨 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>İnkaların 500 yıl önce tek damla harç veya çimento kullanmadan yaptığı taş duvarların büyük depremlerde bile neden yıkılmadığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5540,53 +5555,53 @@
 #bilgidozu #shorts #tarih #inka #arkeoloji</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #inka #arkeoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, inka duvarları, deprem, cusco, tarih, arkeoloji, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🏛️🪨</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>UNESCO World Heritage Cusco / Inca Architecture: https://en.wikipedia.org/wiki/Inca_architecture</t>
         </is>
       </c>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="n"/>
-      <c r="L88" s="5" t="n"/>
-      <c r="M88" s="5" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
+      <c r="M88" s="8" t="n"/>
     </row>
     <row r="89" ht="42" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>video_64.mp4</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Baykuşlar Karanlıkta Uçarken Nasıl Sıfır Ses Çıkarır? Hayalet Kanat Sırrı! 🦉🌙 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Diğer bütün kuşlar kanat çırparken hışırtı çıkarırken baykuşların zifiri karanlıkta tamamen sessiz uçabildiğini biliyor muydun? Üçlü akustik susturucu kanat yapısını inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5595,53 +5610,53 @@
 #bilgidozu #shorts #baykuş #doğa #hayvanlar</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #baykuş #doğa #hayvanlar #dozdışı</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, baykuş, sessiz uçuş, doğa, hayvanlar, aerodinamik, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🦉🌙</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" s="8" t="inlineStr">
         <is>
           <t>Royal Society Interface / Owl Silent Flight: https://en.wikipedia.org/wiki/Owl</t>
         </is>
       </c>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="n"/>
-      <c r="L89" s="5" t="n"/>
-      <c r="M89" s="5" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
     </row>
     <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>video_65.mp4</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>Tükenmez Kalem Kapağındaki O Küçük Delik Neden Hayat Kurtarır? 🖊️⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Tükenmez kalemlerin kapağındaki o küçük deliğin mürekkep kurumasın diye değil, hayat kurtarmak için açıldığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5650,53 +5665,53 @@
 #bilgidozu #shorts #ilginçbilgiler #tasarım #bilim</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ilginçbilgiler #tasarım #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, tükenmez kalem kapağı, bic cristal, güvenlik deliği, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🖊️⚡</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>ISO 11540 / BIC Cristal Safety Design: https://en.wikipedia.org/wiki/Bic_Cristal</t>
         </is>
       </c>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="n"/>
-      <c r="L90" s="5" t="n"/>
-      <c r="M90" s="5" t="n"/>
+      <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
+      <c r="M90" s="8" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>video_66.mp4</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>Su Değil Sert Kaya Zemini Her Gün 100 Metre Yükselip Alçalan Uydu! 🪐🌋 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>Dünya'da okyanus suları yükselip alçalırken, Jüpiter'in uydusu İo'da suyun değil doğrudan sert kaya zeminin her gün 100 metre yükselip alçaldığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5705,53 +5720,53 @@
 #bilgidozu #shorts #uzay #jüpiter #bilim</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #jüpiter #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, io uydusu, jüpiter, kaya gelgiti, yanardağ, uzay, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🌋</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>NASA Juno &amp; Galileo Mission / Io Facts: https://science.nasa.gov/jupiter/moons/io/</t>
         </is>
       </c>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="n"/>
-      <c r="L91" s="5" t="n"/>
-      <c r="M91" s="5" t="n"/>
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
     </row>
     <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>video_68.mp4</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>2000 Yıllık Deniz Batığından Çıkan Dünyanın İlk Mekanik Bilgisayarı! ⚙️🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>İki bin yıl önce batan bir antik Yunan gemisinden dünyanın ilk mekanik bilgisayarının (Antikythera Düzeneği) çıktığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5760,53 +5775,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antikythera düzeneği, antik bilgisayar, tarih, arkeoloji, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚙️🏛️</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>Nature / UCL Antikythera Research Team: https://www.nature.com/articles/s41598-021-84310-w</t>
         </is>
       </c>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="n"/>
-      <c r="L92" s="5" t="n"/>
-      <c r="M92" s="5" t="n"/>
+      <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
+      <c r="L92" s="8" t="n"/>
+      <c r="M92" s="8" t="n"/>
     </row>
     <row r="93" ht="42" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>video_69.mp4</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>70 Derece Çölde Yuvasını Adımlarını Sayarak Bulan Gümüş Karınca! 🐜☀️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>70 derece sıcaklıktaki Sahra Çölü'nde yaşayan gümüş karıncaların yuvalarını adımlarını sayarak (pedometre) bulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5815,53 +5830,53 @@
 #bilgidozu #shorts #doğa #karınca #hayvanlar</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #karınca #hayvanlar #dozdışı</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, sahra çöl karıncası, adım sayar, doğa, hayvanlar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🐜☀️</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>Science (2006) — Wittlinger et al.: https://www.science.org/doi/10.1126/science.1126912</t>
         </is>
       </c>
-      <c r="J93" s="5" t="n"/>
-      <c r="K93" s="5" t="n"/>
-      <c r="L93" s="5" t="n"/>
-      <c r="M93" s="5" t="n"/>
+      <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
     </row>
     <row r="94" ht="42" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>video_70.mp4</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>Benzin Pompası Depo Dolunca Çipsiz ve Sensörsüz Nasıl Kendi Durur? ⛽⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>Benzin istasyonlarındaki pompa tabancasının deponun tam dolduğunu içinde hiçbir kamera, çip veya elektrikli sensör olmadan nasıl anladığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5870,53 +5885,53 @@
 #bilgidozu #shorts #fizik #mühendislik #bilim</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #mühendislik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, benzin pompası, venturi etkisi, fizik, mühendislik, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⛽⚡</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>PEI / Automatic Shut-Off Nozzle: https://pei.org/wiki_pei/automatic-nozzle/</t>
         </is>
       </c>
-      <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n"/>
-      <c r="L94" s="5" t="n"/>
-      <c r="M94" s="5" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="8" t="n"/>
+      <c r="M94" s="8" t="n"/>
     </row>
     <row r="95" ht="42" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>video_71.mp4</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Satürn'ün Kuzey Kutbundaki Dev Altıgen Fırtınanın Sırrı! 🪐🌪️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Satürn gezegeninin kuzey kutbunda içine iki tane Dünya sığacak büyüklükte kusursuz bir altıgen fırtına döndüğünü biliyor muydun? 32.000 kilometrelik bu dev geometrik fırtınanın sırrını inceliyoruz.
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5925,53 +5940,53 @@
 #bilgidozu #shorts #uzay #satürn #bilim</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #satürn #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, satürn, altıgen fırtına, uzay, astronomi, nasa, cassini, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🪐🌪️</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>NASA Cassini Mission / JPL: https://science.nasa.gov/mission/cassini/</t>
         </is>
       </c>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n"/>
-      <c r="L95" s="5" t="n"/>
-      <c r="M95" s="5" t="n"/>
+      <c r="J95" s="8" t="n"/>
+      <c r="K95" s="8" t="n"/>
+      <c r="L95" s="8" t="n"/>
+      <c r="M95" s="8" t="n"/>
     </row>
     <row r="96" ht="42" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>video_73.mp4</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>Efsanevi Şam Çeliği Kılıçların İçinden Karbon Nanotüp Çıktı! ⚔️🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Yüzyıllar önce üretilen efsanevi Şam çeliği kılıçların içinde modern bilimin ancak elektron mikroskobuyla görebildiği karbon nanotüpler bulunduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -5980,53 +5995,53 @@
 #bilgidozu #shorts #tarih #bilim #teknoloji</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #bilim #teknoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, şam çeliği, karbon nanotüp, tarih, kılıç, bilim, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚔️🔬</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Nature (2006) — Reibold et al., TU Dresden: https://www.nature.com/articles/444286a</t>
         </is>
       </c>
-      <c r="J96" s="5" t="n"/>
-      <c r="K96" s="5" t="n"/>
-      <c r="L96" s="5" t="n"/>
-      <c r="M96" s="5" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
+      <c r="M96" s="8" t="n"/>
     </row>
     <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>video_74.mp4</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>Işığın Kırılmasını Hesaplayıp Böceği Suyla Vuran Keskin Nişancı Balık! 🐟🎯 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Suyun altından dışarıdaki bir böceğe su fırlatarak tam on ikiden vuran okçu balığının ışığın kırılmasını nasıl hesapladığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6035,53 +6050,53 @@
 #bilgidozu #shorts #doğa #hayvanlar #bilim</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #hayvanlar #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, okçu balığı, doğa, hayvanlar, optik kırılma, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🐟🎯</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>PLOS ONE (2012) — Vailati et al. (Archerfish Water Jet): https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0047867</t>
         </is>
       </c>
-      <c r="J97" s="5" t="n"/>
-      <c r="K97" s="5" t="n"/>
-      <c r="L97" s="5" t="n"/>
-      <c r="M97" s="5" t="n"/>
+      <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
     </row>
     <row r="98" ht="42" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>video_75.mp4</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga Fırın Camındaki Delikli Siyah Tel Neden Var? ⚡🪟 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Mikrodalga fırınların ön camındaki o siyah delikli metal ızgaranın içeriyi görmen için değil, seni radyasyondan korumak için konulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6090,53 +6105,53 @@
 #bilgidozu #shorts #fizik #teknoloji #bilim</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #fizik #teknoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, mikrodalga fırın, faraday kafesi, fizik, günlük bilim, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚡🪟</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>IEEE Electromagnetic Shielding / Wikipedia — Faraday Cage: https://en.wikipedia.org/wiki/Faraday_cage</t>
         </is>
       </c>
-      <c r="J98" s="5" t="n"/>
-      <c r="K98" s="5" t="n"/>
-      <c r="L98" s="5" t="n"/>
-      <c r="M98" s="5" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+      <c r="L98" s="8" t="n"/>
+      <c r="M98" s="8" t="n"/>
     </row>
     <row r="99" ht="42" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>video_76.mp4</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>Uzayda Ses Yayılsaydı Güneş Dünya'dan 100 Desibel Tren Gibi Gürlerdi! ☀️🔊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>Uzayda ses yayılmadığı için çok şanslı olduğumuzu, yoksa Güneş'in 150 milyon kilometre öteden bile 100 desibel şiddetinde gürleyeceğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6145,53 +6160,53 @@
 #bilgidozu #shorts #uzay #güneş #bilim</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #güneş #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, güneşin sesi, uzayda ses, astronomi, nasa, güneş, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ☀️🔊</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" s="8" t="inlineStr">
         <is>
           <t>NASA Heliophysics / SOHO — Solar Acoustics: https://sci.esa.int/web/soho/-/30851-solar-interior</t>
         </is>
       </c>
-      <c r="J99" s="5" t="n"/>
-      <c r="K99" s="5" t="n"/>
-      <c r="L99" s="5" t="n"/>
-      <c r="M99" s="5" t="n"/>
+      <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
     </row>
     <row r="100" ht="42" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>video_78.mp4</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>Paskalya Adası'ndaki 80 Tonluk Dev Taş Heykeller Nasıl Yürütüldü? 🗿🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Paskalya Adası'ndaki 80 tonluk dev taş heykellerin tekerlek veya vinç olmadan üç halatla dik vaziyette yürütülerek taşındığını biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6200,53 +6215,53 @@
 #bilgidozu #shorts #tarih #paskalyaadası #arkeoloji</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #paskalyaadası #arkeoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, paskalya adası, moai heykelleri, tarih, arkeoloji, mühendislik, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 🗿🏛️</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" s="8" t="inlineStr">
         <is>
           <t>Journal of Archaeological Science (2012) — Lipo &amp; Hunt (Easter Island Moai): https://en.wikipedia.org/wiki/Moai</t>
         </is>
       </c>
-      <c r="J100" s="5" t="n"/>
-      <c r="K100" s="5" t="n"/>
-      <c r="L100" s="5" t="n"/>
-      <c r="M100" s="5" t="n"/>
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
+      <c r="L100" s="8" t="n"/>
+      <c r="M100" s="8" t="n"/>
     </row>
     <row r="101" ht="42" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>video_79.mp4</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>Elektrikli Yılan Balığı 860 Volt Elektrik Üretirken Kendini Neden Çarpmaz? ⚡🐍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>Elektrikli yılan balığının suyun içinde 860 voltluk ölümcül bir elektriği kendi kendini hiç çarpmadan nasıl ürettiğini biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6255,53 +6270,53 @@
 #bilgidozu #shorts #doğa #hayvanlar #bilim</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #hayvanlar #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, elektrikli yılan balığı, elektrosit, doğa, hayvanlar, biyoloji, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! ⚡🐍</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>Nature Communications (2019) — de Santana et al. (860V Electric Eel): https://www.nature.com/articles/s41467-019-11622-9</t>
         </is>
       </c>
-      <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n"/>
-      <c r="L101" s="5" t="n"/>
-      <c r="M101" s="5" t="n"/>
+      <c r="J101" s="8" t="n"/>
+      <c r="K101" s="8" t="n"/>
+      <c r="L101" s="8" t="n"/>
+      <c r="M101" s="8" t="n"/>
     </row>
     <row r="102" ht="42" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>video_80.mp4</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>Yürüyen Merdiven Kenarındaki Fırçalar Ayakkabı Silmek İçin Değil! 👟⚠️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Yürüyen merdivenlerin iki yanındaki o sert siyah fırçaların ayakkabılarını temizlemen için değil, kıyafetlerin dişlilere sıkışmasını önlemek için konulduğunu biliyor muydun?
 Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın!
@@ -6310,53 +6325,53 @@
 #bilgidozu #shorts #ilginçbilgiler #mühendislik #bilim</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ilginçbilgiler #mühendislik #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, yürüyen merdiven fırçası, güvenlik, mühendislik, günlük bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>Bunu daha önce duyanlar 1, ilk kez öğrenenler 2 yazsın! 👟⚠️</t>
         </is>
       </c>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I102" s="8" t="inlineStr">
         <is>
           <t>ASME A17.1 Escalator Safety Code — Escalator Skirt Deflector Brushes: https://en.wikipedia.org/wiki/Escalator</t>
         </is>
       </c>
-      <c r="J102" s="5" t="n"/>
-      <c r="K102" s="5" t="n"/>
-      <c r="L102" s="5" t="n"/>
-      <c r="M102" s="5" t="n"/>
+      <c r="J102" s="8" t="n"/>
+      <c r="K102" s="8" t="n"/>
+      <c r="L102" s="8" t="n"/>
+      <c r="M102" s="8" t="n"/>
     </row>
     <row r="103" ht="42" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>video_81.mp4</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>Neptün ve Uranüs'te Gökyüzünden Gerçek Elmas Yağıyor! 💎🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>Neptün ve Uranüs atmosferindeki yüksek basınç karbon atomlarını sıkıştırarak gerçek elmasa dönüştürür.
 Peki sizce insanoğlu bir gün bu gezegenlerden elmas toplayabilir mi? Yorumlara yazın! 👇
@@ -6365,53 +6380,53 @@
 #bilgidozu #shorts #uzay #bilim #gezegenler</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #gezegenler #dozdışı</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, uzay, neptün, uranüs, elmas yağmuru, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Peki sizce insanoğlu bir gün bu gezegenlerden elmas toplayabilir mi? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>Nature Astronomy / SLAC — Diamond Rain on Ice Giants: https://www6.slac.stanford.edu/news/2017-08-21-scientists-create-diamond-rain-forms-interior-icy-giant-planets</t>
         </is>
       </c>
-      <c r="J103" s="5" t="n"/>
-      <c r="K103" s="5" t="n"/>
-      <c r="L103" s="5" t="n"/>
-      <c r="M103" s="5" t="n"/>
+      <c r="J103" s="8" t="n"/>
+      <c r="K103" s="8" t="n"/>
+      <c r="L103" s="8" t="n"/>
+      <c r="M103" s="8" t="n"/>
     </row>
     <row r="104" ht="42" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>video_82.mp4</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>Uzay Boşluğunda Bile Hayatta Kalan Canlı: Su Ayısı Tardigrad! 🐻🌌 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>Mikroskobik su ayısı Tardigrad, kriptobiyoz özelliği sayesinde uzay boşluğunda ve radyasyonda bile hayatta kalabilir.
 Sizce Dünya'daki en dayanıklı canlı Tardigrad mı yoksa başka bir tür mü? Yorumlarda buluşalım! 👇
@@ -6420,53 +6435,53 @@
 #bilgidozu #shorts #doğa #bilim #tardigrad</t>
         </is>
       </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #bilim #tardigrad #dozdışı</t>
         </is>
       </c>
-      <c r="F104" s="5" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, tardigrad, su ayısı, doğa, uzay, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G104" s="5" t="inlineStr">
+      <c r="G104" s="8" t="inlineStr">
         <is>
           <t>Sizce Dünya'daki en dayanıklı canlı Tardigrad mı yoksa başka bir tür mü? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I104" s="8" t="inlineStr">
         <is>
           <t>ESA FOTON-M3 / Current Biology — Tardigrades in Space: https://en.wikipedia.org/wiki/Tardigrade</t>
         </is>
       </c>
-      <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n"/>
-      <c r="L104" s="5" t="n"/>
-      <c r="M104" s="5" t="n"/>
+      <c r="J104" s="8" t="n"/>
+      <c r="K104" s="8" t="n"/>
+      <c r="L104" s="8" t="n"/>
+      <c r="M104" s="8" t="n"/>
     </row>
     <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>video_84.mp4</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>Tek Bir Ağaçtan Oluşan 47 Bin Gövdeli Dev Orman: Pando! 🌲🌍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>Utah'taki Pando ormanı aslında 47 bin ayrı ağaç değil, yer altındaki tek bir kök sisteminden çıkan dev bir organizmadır.
 Bu ormanı ilk gördüğünüzde tek bir canlı olduğunu tahmin eder miydiniz? Yorumlara yazın! 👇
@@ -6475,53 +6490,53 @@
 #bilgidozu #shorts #doğa #orman #bilim</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #orman #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, pando ormanı, doğa, ağaç, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>Bu ormanı ilk gördüğünüzde tek bir canlı olduğunu tahmin eder miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I105" s="8" t="inlineStr">
         <is>
           <t>USDA Forest Service — Pando Clonal Colony: https://www.fs.usda.gov/detail/fishlake/home/?cid=stelprdb5444544</t>
         </is>
       </c>
-      <c r="J105" s="5" t="n"/>
-      <c r="K105" s="5" t="n"/>
-      <c r="L105" s="5" t="n"/>
-      <c r="M105" s="5" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+      <c r="L105" s="8" t="n"/>
+      <c r="M105" s="8" t="n"/>
     </row>
     <row r="106" ht="42" customHeight="1">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>video_85.mp4</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>Yıldırım Yukarıdan Düşmez: Parlama Yerden Gökyüzüne Çıkar! ⚡🌩️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>Buluttan inen öncü akım yere yaklaştığında, yerden yükselen pozitif yüklerle birleşir ve gördüğümüz ana parlama yerden gökyüzüne çıkar.
 Yıldırımın yerden yukarı çıktığını ilk kez mi duydunuz? Yorumlarda belirtin! 👇
@@ -6530,53 +6545,53 @@
 #bilgidozu #shorts #bilim #yıldırım #doğaolayları</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim #yıldırım #doğaolayları #dozdışı</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr">
+      <c r="F106" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, yıldırım, günlük bilim, fizik, doğa olayları, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr">
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>Yıldırımın yerden yukarı çıktığını ilk kez mi duydunuz? Yorumlarda belirtin! 👇</t>
         </is>
       </c>
-      <c r="H106" s="5" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>NOAA Severe Weather — Lightning Return Stroke Physics: https://www.weather.gov/safety/lightning-science</t>
         </is>
       </c>
-      <c r="J106" s="5" t="n"/>
-      <c r="K106" s="5" t="n"/>
-      <c r="L106" s="5" t="n"/>
-      <c r="M106" s="5" t="n"/>
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
+      <c r="L106" s="8" t="n"/>
+      <c r="M106" s="8" t="n"/>
     </row>
     <row r="107" ht="42" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>video_86.mp4</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>Jüpiter'de Dünya'dan Büyük 300 Yıllık Fırtına: Büyük Kırmızı Leke! 🌪️🪐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>Jüpiter'deki Büyük Kırmızı Leke, içine Dünya'yı sığdırabilecek büyüklükte ve en az 300 yıldır aralıksız dönen bir fırtınadır.
 Sizce Jüpiter'deki bu dev fırtına bir gün tamamen durur mu? Tahmininizi yorumlara yazın! 👇
@@ -6585,53 +6600,53 @@
 #bilgidozu #shorts #uzay #jüpiter #bilim</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #jüpiter #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, jüpiter, büyük kırmızı leke, uzay, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>Sizce Jüpiter'deki bu dev fırtına bir gün tamamen durur mu? Tahmininizi yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I107" s="8" t="inlineStr">
         <is>
           <t>NASA Juno Mission — Jupiter Great Red Spot: https://science.nasa.gov/jupiter/facts/</t>
         </is>
       </c>
-      <c r="J107" s="5" t="n"/>
-      <c r="K107" s="5" t="n"/>
-      <c r="L107" s="5" t="n"/>
-      <c r="M107" s="5" t="n"/>
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
+      <c r="L107" s="8" t="n"/>
+      <c r="M107" s="8" t="n"/>
     </row>
     <row r="108" ht="42" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>video_87.mp4</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>Everest'in 3 Katı Yüksekliğinde Dev Yanardağ: Olympus Mons! 🌋🔴 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>Mars'taki Olympus Mons yanardağı yaklaşık 22 kilometre yüksekliğiyle Everest Dağı'nın tam 3 katı büyüklüğündedir.
 Everest'in üç katı yüksekliğinde bir dağın zirvesine çıkmak ister miydiniz? Yorumlara yazın! 👇
@@ -6640,53 +6655,53 @@
 #bilgidozu #shorts #mars #uzay #bilim</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #mars #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, mars, olympus mons, yanardağ, uzay, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G108" s="5" t="inlineStr">
+      <c r="G108" s="8" t="inlineStr">
         <is>
           <t>Everest'in üç katı yüksekliğinde bir dağın zirvesine çıkmak ister miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
+      <c r="I108" s="8" t="inlineStr">
         <is>
           <t>NASA Mars Exploration — Olympus Mons: https://science.nasa.gov/mars/facts/</t>
         </is>
       </c>
-      <c r="J108" s="5" t="n"/>
-      <c r="K108" s="5" t="n"/>
-      <c r="L108" s="5" t="n"/>
-      <c r="M108" s="5" t="n"/>
+      <c r="J108" s="8" t="n"/>
+      <c r="K108" s="8" t="n"/>
+      <c r="L108" s="8" t="n"/>
+      <c r="M108" s="8" t="n"/>
     </row>
     <row r="109" ht="42" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>video_88.mp4</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>Beyni ve Kanı Olmadan Denizde Avlanan Canlı: Denizyıldızı! ⭐🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>Denizyıldızlarının merkezi bir beyni ve kanı yoktur; damarlarında kalp yerine pompalanan filtre edilmiş deniz suyu dolaşır.
 Beyni ve kanı olmadan yaşayan bu canlı hakkında siz ne düşünüyorsunuz? Yorumlara yazın! 👇
@@ -6695,53 +6710,53 @@
 #bilgidozu #shorts #doğa #okyanus #bilim</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #okyanus #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, denizyıldızı, okyanus, doğa, hayvanlar, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>Beyni ve kanı olmadan yaşayan bu canlı hakkında siz ne düşünüyorsunuz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="8" t="inlineStr">
         <is>
           <t>Smithsonian Ocean / Wikipedia — Sea Stars Anatomy: https://en.wikipedia.org/wiki/Starfish</t>
         </is>
       </c>
-      <c r="J109" s="5" t="n"/>
-      <c r="K109" s="5" t="n"/>
-      <c r="L109" s="5" t="n"/>
-      <c r="M109" s="5" t="n"/>
+      <c r="J109" s="8" t="n"/>
+      <c r="K109" s="8" t="n"/>
+      <c r="L109" s="8" t="n"/>
+      <c r="M109" s="8" t="n"/>
     </row>
     <row r="110" ht="42" customHeight="1">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>video_89.mp4</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>Yunuslar Tek Gözü Açık ve Yarım Beyinle Nasıl Uyur? 🐬🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D110" s="8" t="inlineStr">
         <is>
           <t>Yunuslar uykuda boğulmamak için beyinlerinin sadece bir yarısını uyuturken diğer yarısıyla nefes alıp çevreyi gözetler.
 Beyninizin yarısını uyutup diğer yarısıyla uyanık kalmak ister miydiniz? Yorumlara yazın! 👇
@@ -6750,53 +6765,53 @@
 #bilgidozu #shorts #yunus #doğa #bilim</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #yunus #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F110" s="5" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, yunuslar, doğa, hayvanlar alemi, uyku, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G110" s="5" t="inlineStr">
+      <c r="G110" s="8" t="inlineStr">
         <is>
           <t>Beyninizin yarısını uyutup diğer yarısıyla uyanık kalmak ister miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H110" s="5" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I110" s="5" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
         <is>
           <t>Sleep Foundation / Wikipedia — Unihemispheric Slow-Wave Sleep: https://en.wikipedia.org/wiki/Unihemispheric_slow-wave_sleep</t>
         </is>
       </c>
-      <c r="J110" s="5" t="n"/>
-      <c r="K110" s="5" t="n"/>
-      <c r="L110" s="5" t="n"/>
-      <c r="M110" s="5" t="n"/>
+      <c r="J110" s="8" t="n"/>
+      <c r="K110" s="8" t="n"/>
+      <c r="L110" s="8" t="n"/>
+      <c r="M110" s="8" t="n"/>
     </row>
     <row r="111" ht="42" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>video_90.mp4</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>Dev Bir Okyanusa Bırakılsa Suda Yüzecek Gezegen: Satürn! 🪐🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>Satürn'ün ortalama yoğunluğu santimetreküp başına 0,68 gramdır; yani sudan daha hafif olduğu için dev bir okyanusta yüzebilir.
 Koca bir gezegenin sudan daha hafif olması sizi de şaşırttı mı? Yorumlara yazın! 👇
@@ -6805,53 +6820,53 @@
 #bilgidozu #shorts #satürn #uzay #bilim</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E111" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #satürn #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, satürn, uzay, gezegenler, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G111" s="8" t="inlineStr">
         <is>
           <t>Koca bir gezegenin sudan daha hafif olması sizi de şaşırttı mı? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="H111" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I111" s="8" t="inlineStr">
         <is>
           <t>NASA Cassini Mission — Saturn Planetary Density: https://science.nasa.gov/saturn/facts/</t>
         </is>
       </c>
-      <c r="J111" s="5" t="n"/>
-      <c r="K111" s="5" t="n"/>
-      <c r="L111" s="5" t="n"/>
-      <c r="M111" s="5" t="n"/>
+      <c r="J111" s="8" t="n"/>
+      <c r="K111" s="8" t="n"/>
+      <c r="L111" s="8" t="n"/>
+      <c r="M111" s="8" t="n"/>
     </row>
     <row r="112" ht="42" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>video_92.mp4</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
         <is>
           <t>Cam Zamanla Akan Bir Sıvı Değil: En Büyük Bilim Efsanesi! 🪟🔬 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D112" s="8" t="inlineStr">
         <is>
           <t>Cam çok yavaş akan bir sıvı değil, amorf bir katıdır; eski pencerelerin altının kalın olması üretim tekniğinden kaynaklanır.
 Siz de okulda camın çok yavaş akan bir sıvı olduğunu duymuş muydunuz? Yorumlarda belirtin! 👇
@@ -6860,53 +6875,53 @@
 #bilgidozu #shorts #bilim #fizik #ilginçbilgiler</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #bilim #fizik #ilginçbilgiler #dozdışı</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, cam, fizik, günlük bilim, şehir efsanesi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G112" s="5" t="inlineStr">
+      <c r="G112" s="8" t="inlineStr">
         <is>
           <t>Siz de okulda camın çok yavaş akan bir sıvı olduğunu duymuş muydunuz? Yorumlarda belirtin! 👇</t>
         </is>
       </c>
-      <c r="H112" s="5" t="inlineStr">
+      <c r="H112" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I112" s="5" t="inlineStr">
+      <c r="I112" s="8" t="inlineStr">
         <is>
           <t>American Journal of Physics (Zanotto, 1998) — Do Cathedral Glasses Flow?: https://en.wikipedia.org/wiki/Glass</t>
         </is>
       </c>
-      <c r="J112" s="5" t="n"/>
-      <c r="K112" s="5" t="n"/>
-      <c r="L112" s="5" t="n"/>
-      <c r="M112" s="5" t="n"/>
+      <c r="J112" s="8" t="n"/>
+      <c r="K112" s="8" t="n"/>
+      <c r="L112" s="8" t="n"/>
+      <c r="M112" s="8" t="n"/>
     </row>
     <row r="113" ht="42" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>video_93.mp4</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>Ay Her Yıl Dünya'dan 3,8 Santimetre Uzaklaşıyor! 🌕🚀 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>Apollo astronotlarının bıraktığı lazer aynaları, Ay'ın gelgit kuvvetleri nedeniyle her yıl 3,8 cm uzaklaştığını kanıtlamıştır.
 Peki Ay'ın her yıl bizden uzaklaşması gelecekte Dünya'yı sizce nasıl etkiler? Yorumlara yazın! 👇
@@ -6915,53 +6930,53 @@
 #bilgidozu #shorts #ay #uzay #bilim</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #ay #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, ay, dünya, uzay, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="G113" s="8" t="inlineStr">
         <is>
           <t>Peki Ay'ın her yıl bizden uzaklaşması gelecekte Dünya'yı sizce nasıl etkiler? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H113" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I113" s="8" t="inlineStr">
         <is>
           <t>NASA — Lunar Laser Ranging Experiment: https://science.nasa.gov/moon/facts/</t>
         </is>
       </c>
-      <c r="J113" s="5" t="n"/>
-      <c r="K113" s="5" t="n"/>
-      <c r="L113" s="5" t="n"/>
-      <c r="M113" s="5" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
+      <c r="L113" s="8" t="n"/>
+      <c r="M113" s="8" t="n"/>
     </row>
     <row r="114" ht="42" customHeight="1">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>video_94.mp4</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>Yetişkin Kediler Birbirine Değil Sadece İnsanlara Miyavlar! 🐱🔊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>Yetişkin kediler kendi aralarında koku ve beden diliyle anlaşır; miyavlama sesini sadece insanlarla iletişim kurmak için kullanır.
 Sizin kediniz bir şey istediğinde nasıl sesler çıkarıyor? Yorumlarda anlatın! 👇
@@ -6970,53 +6985,53 @@
 #bilgidozu #shorts #kediler #hayvanlar #doğa</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E114" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #kediler #hayvanlar #doğa #dozdışı</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, kediler, kedi miyavlaması, doğa, hayvanlar, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G114" s="8" t="inlineStr">
         <is>
           <t>Sizin kediniz bir şey istediğinde nasıl sesler çıkarıyor? Yorumlarda anlatın! 👇</t>
         </is>
       </c>
-      <c r="H114" s="5" t="inlineStr">
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>Cornell Feline Health Center / Wikipedia — Cat Vocalization: https://en.wikipedia.org/wiki/Cat_communication</t>
         </is>
       </c>
-      <c r="J114" s="5" t="n"/>
-      <c r="K114" s="5" t="n"/>
-      <c r="L114" s="5" t="n"/>
-      <c r="M114" s="5" t="n"/>
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
+      <c r="L114" s="8" t="n"/>
+      <c r="M114" s="8" t="n"/>
     </row>
     <row r="115" ht="42" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>video_95.mp4</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>Dünya Uzayda Saniyede 30 Kilometre Hızla Uçuyor! 🌍⚡ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Dünya Güneş etrafındaki yörüngesinde saniyede 30 km, yani saatte 108 bin km hızla ilerler.
 Dünya'nın uzayda saniyede otuz kilometre hızla uçtuğunu bilmek başınızı döndürdü mü? Yorumlara yazın! 👇
@@ -7025,53 +7040,53 @@
 #bilgidozu #shorts #dünya #uzay #bilim</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E115" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #dünya #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F115" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, dünya, uzay, güneş sistemi, hız, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="G115" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın uzayda saniyede otuz kilometre hızla uçtuğunu bilmek başınızı döndürdü mü? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>NASA Earth Fact Sheet — Orbital Velocity: https://science.nasa.gov/earth/facts/</t>
         </is>
       </c>
-      <c r="J115" s="5" t="n"/>
-      <c r="K115" s="5" t="n"/>
-      <c r="L115" s="5" t="n"/>
-      <c r="M115" s="5" t="n"/>
+      <c r="J115" s="8" t="n"/>
+      <c r="K115" s="8" t="n"/>
+      <c r="L115" s="8" t="n"/>
+      <c r="M115" s="8" t="n"/>
     </row>
     <row r="116" ht="42" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
         <is>
           <t>video_96.mp4</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
+      <c r="C116" s="8" t="inlineStr">
         <is>
           <t>Mısır Piramitlerinden Çıkan 3000 Yıllık Yenebilir Bal! 🍯🏺 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>Mısır firavun mezarlarında bulunan 3000 yıllık mühürlü bal küpleri, düşük nem ve asidik yapı sayesinde bozulmadan kalmıştır.
 Peki üç bin yıllık bir mezardan çıkan balı tatmaya cesaret eder miydiniz? Yorumlara yazın! 👇
@@ -7080,53 +7095,53 @@
 #bilgidozu #shorts #tarih #mısır #bilim</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #mısır #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
+      <c r="F116" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, mısır piramitleri, bal, tarih, arkeoloji, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G116" s="5" t="inlineStr">
+      <c r="G116" s="8" t="inlineStr">
         <is>
           <t>Peki üç bin yıllık bir mezardan çıkan balı tatmaya cesaret eder miydiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H116" s="5" t="inlineStr">
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Arkeoloji</t>
         </is>
       </c>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="I116" s="8" t="inlineStr">
         <is>
           <t>Smithsonian Magazine — The Science Behind Honey's Eternal Shelf Life: https://en.wikipedia.org/wiki/Honey</t>
         </is>
       </c>
-      <c r="J116" s="5" t="n"/>
-      <c r="K116" s="5" t="n"/>
-      <c r="L116" s="5" t="n"/>
-      <c r="M116" s="5" t="n"/>
+      <c r="J116" s="8" t="n"/>
+      <c r="K116" s="8" t="n"/>
+      <c r="L116" s="8" t="n"/>
+      <c r="M116" s="8" t="n"/>
     </row>
     <row r="117" ht="42" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>video_97.mp4</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın Çekirdeği Güneş Yüzeyi Kadar Sıcak: 5400 Derece! 🌋🔥 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın iç çekirdeği yaklaşık 5400 santigrat derece sıcaklığıyla Güneş'in yüzeyi kadar sıcaktır ancak dev basınç nedeniyle katıdır.
 Ayaklarımızın altında Güneş kadar sıcak bir çekirdek olması sizi de şaşırttı mı? Yorumlarda buluşalım! 👇
@@ -7135,53 +7150,53 @@
 #bilgidozu #shorts #dünya #bilim #jeoloji</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #dünya #bilim #jeoloji #dozdışı</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, dünya çekirdeği, güneş, jeoloji, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G117" s="8" t="inlineStr">
         <is>
           <t>Ayaklarımızın altında Güneş kadar sıcak bir çekirdek olması sizi de şaşırttı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H117" s="8" t="inlineStr">
         <is>
           <t>Fizik ve Mühendislik</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>Science / Wikipedia — Earth's Inner Core Temperature: https://en.wikipedia.org/wiki/Earth%27s_inner_core</t>
         </is>
       </c>
-      <c r="J117" s="5" t="n"/>
-      <c r="K117" s="5" t="n"/>
-      <c r="L117" s="5" t="n"/>
-      <c r="M117" s="5" t="n"/>
+      <c r="J117" s="8" t="n"/>
+      <c r="K117" s="8" t="n"/>
+      <c r="L117" s="8" t="n"/>
+      <c r="M117" s="8" t="n"/>
     </row>
     <row r="118" ht="42" customHeight="1">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>video_98.mp4</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C118" s="8" t="inlineStr">
         <is>
           <t>Filler Kilometrelerce Uzaktaki Sesi Ayak Tabanıyla Duyar! 🐘🌍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>Filler çıkardıkları düşük frekanslı seslerin topraktaki sismik titreşimlerini hassas ayak tabanlarıyla kilometrelerce uzaktan algılar.
 Fillerin ayak tabanlarıyla yeri dinleyerek anlaşması hakkında ne düşünüyorsunuz? Yorumlara yazın! 👇
@@ -7190,53 +7205,53 @@
 #bilgidozu #shorts #filler #doğa #bilim</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #filler #doğa #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F118" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, filler, doğa, hayvanlar, sismik ses, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G118" s="8" t="inlineStr">
         <is>
           <t>Fillerin ayak tabanlarıyla yeri dinleyerek anlaşması hakkında ne düşünüyorsunuz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Canlılar</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>Stanford University / Wikipedia — Elephant Seismic Communication: https://en.wikipedia.org/wiki/Elephant_cognition</t>
         </is>
       </c>
-      <c r="J118" s="5" t="n"/>
-      <c r="K118" s="5" t="n"/>
-      <c r="L118" s="5" t="n"/>
-      <c r="M118" s="5" t="n"/>
+      <c r="J118" s="8" t="n"/>
+      <c r="K118" s="8" t="n"/>
+      <c r="L118" s="8" t="n"/>
+      <c r="M118" s="8" t="n"/>
     </row>
     <row r="119" ht="42" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>video_99.mp4</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>Yan Yatarak Dönen Gezegen Uranüs'te 1 Gece 42 Yıl Sürüyor! 🪐❄️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D119" s="8" t="inlineStr">
         <is>
           <t>Yörüngesinde 98 derece yan yatmış olan Uranüs'ün kutuplarında bir gündüz ve bir gece aralıksız 42 Dünya yılı sürer.
 Kırk iki yıl süren bir gecede mi yoksa kırk iki yıl süren gündüzde mi yaşamak isterdiniz? Yorumlara yazın! 👇
@@ -7245,53 +7260,53 @@
 #bilgidozu #shorts #uranüs #uzay #bilim</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uranüs #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, uranüs, uzay, gezegenler, astronomi, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="G119" s="8" t="inlineStr">
         <is>
           <t>Kırk iki yıl süren bir gecede mi yoksa kırk iki yıl süren gündüzde mi yaşamak isterdiniz? Yorumlara yazın! 👇</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Evren</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I119" s="8" t="inlineStr">
         <is>
           <t>NASA — Uranus Planetary Fact Sheet: https://science.nasa.gov/uranus/facts/</t>
         </is>
       </c>
-      <c r="J119" s="5" t="n"/>
-      <c r="K119" s="5" t="n"/>
-      <c r="L119" s="5" t="n"/>
-      <c r="M119" s="5" t="n"/>
+      <c r="J119" s="8" t="n"/>
+      <c r="K119" s="8" t="n"/>
+      <c r="L119" s="8" t="n"/>
+      <c r="M119" s="8" t="n"/>
     </row>
     <row r="120" ht="42" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>video_101.mp4</t>
         </is>
       </c>
-      <c r="C120" s="5" t="inlineStr">
+      <c r="C120" s="8" t="inlineStr">
         <is>
           <t>Güneş Bir Saniyeliğine Sönseydi Ne Olurdu? ☀️🌑 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="D120" s="8" t="inlineStr">
         <is>
           <t>Şu an başını kaldırıp gökyüzüne baktığında, Güneş'in hâlâ orada olduğundan gerçekten emin misin? Ya tam şu saniye sessizce söndüyse? İşin en ürpertici kısmı ne biliyor musun? Bunu tam sekiz dakika yirmi saniye boyunca ruhun bile duymayacak. Çünkü Güneş'ten çıkan son ışık gözüne ulaşana kadar gökyüzü masmavi kalır. Ama sekizinci dakikanın sonunda gökyüzü bir anda zifiri karanlığa gömülür ve Dünya yörüngeden kopup buzlu boşluğa savrulur. Peki sen o son sekiz dakikayı dışarıda gökyüzünü izleyerek mi geçirirdin, yoksa yeraltı sığınaklarına inerek mi? Yorumlarda buluşalım.
 💬 Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇
@@ -7300,53 +7315,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F120" s="5" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, güneş, uzay, kozmik felaket, astronomi, bilim, dünya, ışık hızı, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G120" s="5" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>Peki böyle bir kırılma anında sen sekiz dakikalık son gün ışığını dışarıda izlemeyi mi seçerdin, yoksa doğrudan yeraltı sığınaklarına inmeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H120" s="5" t="inlineStr">
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I120" s="5" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Sunlight (Işık Hızı ve Güneş Işığı Süresi): https://en.wikipedia.org/wiki/Sunlight</t>
         </is>
       </c>
-      <c r="J120" s="5" t="n"/>
-      <c r="K120" s="5" t="n"/>
-      <c r="L120" s="5" t="n"/>
-      <c r="M120" s="5" t="n"/>
+      <c r="J120" s="8" t="n"/>
+      <c r="K120" s="8" t="n"/>
+      <c r="L120" s="8" t="n"/>
+      <c r="M120" s="8" t="n"/>
     </row>
     <row r="121" ht="42" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>video_102.mp4</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C121" s="8" t="inlineStr">
         <is>
           <t>Ay Dünya'ya Yaklaşsaydı Okyanuslara Ne Olurdu? 🌕🌊 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D121" s="8" t="inlineStr">
         <is>
           <t>Gece gökyüzüne baktığında, Ay'ın hep aynı yerde durduğunu sanıyorsun değil mi? Peki ya Ay Dünya'ya doğru yaklaşmaya başlasaydı ne olurdu? İlk başta gökyüzünde devasa görünürdü ama hemen ardından kütle çekim kabusu başlardı. Okyanuslar yüzlerce metre yükselip kıyı şehirlerini yutardı. Dünya'ya on sekiz bin kilometre mesafedeki Roche sınırına girdiği anda ise Ay gökyüzünde paramparça olur ve Dünya'nın etrafında tıpkı Satürn gibi parlak bir halka oluştururdu. Peki sen gökyüzünde Satürn gibi dev bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım.
 💬 Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇
@@ -7355,53 +7370,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
+      <c r="F121" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, ay, dünya, roche sınırı, satürn, uzay, astronomi, bilim, kozmik felaket, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G121" s="8" t="inlineStr">
         <is>
           <t>Peki sen gökyüzünde dev bir Ay yerine Satürn gibi muazzam bir halka görmeyi mi isterdin, yoksa Ay'ın olduğu yerde kalmasını mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H121" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I121" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Roche Limit (Gelgit Parçalanma Sınırı): https://en.wikipedia.org/wiki/Roche_limit</t>
         </is>
       </c>
-      <c r="J121" s="5" t="n"/>
-      <c r="K121" s="5" t="n"/>
-      <c r="L121" s="5" t="n"/>
-      <c r="M121" s="5" t="n"/>
+      <c r="J121" s="8" t="n"/>
+      <c r="K121" s="8" t="n"/>
+      <c r="L121" s="8" t="n"/>
+      <c r="M121" s="8" t="n"/>
     </row>
     <row r="122" ht="42" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>video_103.mp4</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C122" s="8" t="inlineStr">
         <is>
           <t>Uzayda Ağlarsan Gözyaşların Neden Yanağından Akmaz? 🧑‍🚀💧 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D122" s="8" t="inlineStr">
         <is>
           <t>Uzayda tek başına süzülürken bir anda ağlamaya başlasan gözyaşlarının yanağından aşağı süzüleceğini mi sanıyorsun? Hiç de öyle olmaz. Dünya'da gözyaşını aşağı çeken şey yerçekimidir. Ama uzayın ağırlıksız boşluğunda, su moleküllerini birbirine kenetleyen yüzey gerilimi tek patron haline gelir. Gözünden çıkan her damla, akmak yerine göz pınarının tam üzerinde şeffaf, titreyen bir su küresine dönüşür ve sen bir bezle silene kadar yüzünden asla ayrılmaz. Peki sen yerçekimsiz ortamda yaşamayı deneyimlemek mi isterdin, yoksa ayağının yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım.
 💬 Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇
@@ -7410,53 +7425,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="E122" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="F122" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, uzay, astronot, yerçekimi, yüzey gerilimi, bilim, fizik, uzay istasyonu, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G122" s="8" t="inlineStr">
         <is>
           <t>Peki sen yerçekimsiz ortamda haftalarca yaşamayı deneyimlemek mi isterdin, yoksa ayağının sağlamca yere bastığı Dünya'da kalmayı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="H122" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="I122" s="8" t="inlineStr">
         <is>
           <t>CSA / Wikipedia — Surface Tension in Microgravity (Uzayda Yüzey Gerilimi): https://en.wikipedia.org/wiki/Surface_tension</t>
         </is>
       </c>
-      <c r="J122" s="5" t="n"/>
-      <c r="K122" s="5" t="n"/>
-      <c r="L122" s="5" t="n"/>
-      <c r="M122" s="5" t="n"/>
+      <c r="J122" s="8" t="n"/>
+      <c r="K122" s="8" t="n"/>
+      <c r="L122" s="8" t="n"/>
+      <c r="M122" s="8" t="n"/>
     </row>
     <row r="123" ht="42" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>video_104.mp4</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C123" s="8" t="inlineStr">
         <is>
           <t>Dünya'ya 50 Işık Yılı Mesafede Süpernova Patlasa Ne Olur? 💥🌟 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D123" s="8" t="inlineStr">
         <is>
           <t>Gündüz vakti masmavi gökyüzünde bir anda ikinci bir Güneş'in parladığını hayal et. Dünya'ya elli ışık yılı mesafede dev bir yıldız süpernova olarak patlasaydı tam olarak bunu yaşardık. Haftalarca geceleri bile gökyüzü hiç kararmazdı. Ama asıl tehlike o parlak ışık değil, görünmez gama ışınları olurdu. Üst atmosferdeki ozon tabakası hızla erir ve yüzeye inen radyasyon okyanuslardaki besin zincirini altüst ederdi. Peki böyle bir kozmik patlama görsen, önce teleskopla izlemeye mi koşardın yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım.
 💬 Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇
@@ -7465,53 +7480,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E123" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F123" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, süpernova, uzay, gama ışınları, kozmik felaket, yıldız, astronomi, bilim, dünya, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G123" s="5" t="inlineStr">
+      <c r="G123" s="8" t="inlineStr">
         <is>
           <t>Peki böyle bir kozmik patlama görsen önce teleskopla izlemeye mi koşardın, yoksa radyasyondan korunacak bir yer mi arardın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="H123" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I123" s="5" t="inlineStr">
+      <c r="I123" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Near-Earth Supernova (Yakın Süpernova Etkileri): https://en.wikipedia.org/wiki/Near-Earth_supernova</t>
         </is>
       </c>
-      <c r="J123" s="5" t="n"/>
-      <c r="K123" s="5" t="n"/>
-      <c r="L123" s="5" t="n"/>
-      <c r="M123" s="5" t="n"/>
+      <c r="J123" s="8" t="n"/>
+      <c r="K123" s="8" t="n"/>
+      <c r="L123" s="8" t="n"/>
+      <c r="M123" s="8" t="n"/>
     </row>
     <row r="124" ht="42" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>video_105.mp4</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
+      <c r="C124" s="8" t="inlineStr">
         <is>
           <t>Bir Çay Kaşığı Nötron Yıldızı Dünya'ya Düşse Ne Olur? 🥄🌌 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D124" s="8" t="inlineStr">
         <is>
           <t>Elindeki küçücük bir çay kaşığının Everest Dağı kadar ağır olabileceğini hayal edebilir misin? Evrenin en ekstrem canavarı olan nötron yıldızlarıyla tanış. Dev bir yıldız çöktüğünde çekirdeği o kadar korkunç sıkışır ki, koca bir Güneş sadece yirmi kilometre çapında bir küreye hapsolur. Bu yıldızdan alacağın tek bir çay kaşığı madde tam bir milyar ton ağırlığındadır. Onu Dünya'da elinden bıraksan toprağı ve kayaları delip doğrudan gezegenin çekirdeğine kadar batardı. Peki seni uzayda en çok büyüleyen şey, kara delikler mi yoksa nötron yıldızları mı? Yorumlarda buluşalım.
 💬 Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇
@@ -7520,53 +7535,53 @@
 #bilgidozu #shorts #uzay #bilim</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr">
+      <c r="E124" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #uzay #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="F124" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, nötron yıldızı, kara delik, uzay, astronomi, fizik, bilim, evren, ilginç bilgiler, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G124" s="8" t="inlineStr">
         <is>
           <t>Peki seni uzayda en çok büyüleyen şey her şeyi yutan kara delikler mi, yoksa bu inanılmaz yoğunluktaki nötron yıldızları mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H124" s="5" t="inlineStr">
+      <c r="H124" s="8" t="inlineStr">
         <is>
           <t>Uzay ve Astronomi</t>
         </is>
       </c>
-      <c r="I124" s="5" t="inlineStr">
+      <c r="I124" s="8" t="inlineStr">
         <is>
           <t>NASA / Wikipedia — Neutron Star (Nötron Yıldızı Yoğunluğu): https://en.wikipedia.org/wiki/Neutron_star</t>
         </is>
       </c>
-      <c r="J124" s="5" t="n"/>
-      <c r="K124" s="5" t="n"/>
-      <c r="L124" s="5" t="n"/>
-      <c r="M124" s="5" t="n"/>
+      <c r="J124" s="8" t="n"/>
+      <c r="K124" s="8" t="n"/>
+      <c r="L124" s="8" t="n"/>
+      <c r="M124" s="8" t="n"/>
     </row>
     <row r="125" ht="42" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>video_111.mp4</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>Dünya'nın En Issız Noktası Point Nemo: En Yakın İnsanlar Uzayda! 🌊🛰️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>Dünya üzerinde öyle ıssız bir nokta var ki, orada bir tekneyle mahsur kalsan sana en yakın insanlar Dünya'da değil, uzayda olurdu. Güney Pasifik Okyanusu'nun ortasındaki Point Nemo ile tanış. Burası en yakın kara parçasına tam 2.688 kilometre uzaklıktadır. Buna karşılık, Uluslararası Uzay İstasyonu başının sadece 400 kilometre üzerinden geçer. Yani gökyüzündeki astronotlar, sana karadaki insanlardan tam 6 kat daha yakındır. Uzay ajansları da ömrü biten uyduları bu dev su mezarlığına düşürür. Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım!
 💬 Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇
@@ -7575,53 +7590,53 @@
 #bilgidozu #shorts #doğa #okyanus #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E125" s="5" t="inlineStr">
+      <c r="E125" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #doğa #okyanus #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
+      <c r="F125" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, point nemo, güney pasifik, dünyanın en ıssız noktası, uydu mezarlığı, uluslararası uzay istasyonu, coğrafya, doğa, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G125" s="8" t="inlineStr">
         <is>
           <t>Peki sen böyle mutlak bir sessizliğin ortasında tek başına bir gece geçirmeye cesaret edebilir miydin, yoksa kıyıdan asla ayrılmaz mıydın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="H125" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="I125" s="8" t="inlineStr">
         <is>
           <t>NOAA / Wikipedia — Oceanic Pole of Inaccessibility (Point Nemo): https://en.wikipedia.org/wiki/Pole_of_inaccessibility</t>
         </is>
       </c>
-      <c r="J125" s="5" t="n"/>
-      <c r="K125" s="5" t="n"/>
-      <c r="L125" s="5" t="n"/>
-      <c r="M125" s="5" t="n"/>
+      <c r="J125" s="8" t="n"/>
+      <c r="K125" s="8" t="n"/>
+      <c r="L125" s="8" t="n"/>
+      <c r="M125" s="8" t="n"/>
     </row>
     <row r="126" ht="42" customHeight="1">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>video_112.mp4</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C126" s="8" t="inlineStr">
         <is>
           <t>Antarktika'daki Buzuldan Neden Kan Kırmızısı Şelale Akıyor? 🧊🩸 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D126" s="8" t="inlineStr">
         <is>
           <t>Antarktika'nın bembeyaz, dondurucu buzullarının arasından bir anda kıpkırmızı, kan renginde bir şelalenin aktığını görsen ne düşünürdün? Taylor Buzulu'ndaki bu ürpertici manzaranın sebebi kan ya da yosun değil, tam 5 milyon yıl önce buzulun 400 metre altına hapsolmuş antik bir yeraltı gölü. Bu gizli gölün suyu okyanuslardan 3 kat daha tuzlu olduğu için dondurucu soğukta bile asla donmuyor. İçindeki yoğun demir, buzulun çatlaklarından sızıp milyonlarca yıl sonra ilk kez havadaki oksijenle temas ettiği anda saniyeler içinde paslanarak kıpkırmızı bir şelaleye dönüşüyor. Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım!
 💬 Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇
@@ -7630,53 +7645,53 @@
 #bilgidozu #shorts #antarktika #doğa #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E126" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #antarktika #doğa #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="F126" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, kan şelalesi, blood falls, antarktika, taylor buzulu, doğa olayları, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G126" s="8" t="inlineStr">
         <is>
           <t>Peki sen Antarktika'daki bu gizemli buzulun yanına gitmeyi mi seçerdin, yoksa sıcak bir tropik adada kalmayı mı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="H126" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I126" s="5" t="inlineStr">
+      <c r="I126" s="8" t="inlineStr">
         <is>
           <t>NSF / Wikipedia — Blood Falls, Taylor Glacier Antarctica (Kan Şelalesi): https://en.wikipedia.org/wiki/Blood_Falls</t>
         </is>
       </c>
-      <c r="J126" s="5" t="n"/>
-      <c r="K126" s="5" t="n"/>
-      <c r="L126" s="5" t="n"/>
-      <c r="M126" s="5" t="n"/>
+      <c r="J126" s="8" t="n"/>
+      <c r="K126" s="8" t="n"/>
+      <c r="L126" s="8" t="n"/>
+      <c r="M126" s="8" t="n"/>
     </row>
     <row r="127" ht="42" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>video_113.mp4</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="C127" s="8" t="inlineStr">
         <is>
           <t>5,5 Milyon Yıldır Güneş Görmeyen Mühürlü Mağara: Movile! 🕳️🕷️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D127" s="8" t="inlineStr">
         <is>
           <t>Tam 5,5 milyon yıl boyunca güneş ışığının tek bir zerresini bile görmemiş, mühürlü bir yeraltı dünyasının kapısını açtığını hayal et. Romanya'da tesadüfen keşfedilen Movile Mağarası, dış dünyadan tamamen kopuk bambaşka bir gezegen gibi. İçerideki havada oksijen normalin yarısından bile az, atmosferi ise zehirli hidrojen sülfür ve karbondioksitle dolu. Güneş ışığı olmadığı için buradaki yaşam tamamen kimyasal enerjiyle ayakta kalıyor ve içeride gözleri yok olmuş, sadece buraya özgü 30'dan fazla gizemli canlı türü yaşıyor. Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım!
 💬 Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇
@@ -7685,53 +7700,53 @@
 #bilgidozu #shorts #mağara #doğa #biyoloji #bilim</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E127" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #mağara #doğa #biyoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="F127" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, movile mağarası, mühürlü mağara, romanya, kemosentez, gizemli yerler, doğa, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="G127" s="8" t="inlineStr">
         <is>
           <t>Peki özel bir oksijen tüpüyle bu karanlık mağaraya inme şansın olsa içeri adım atar mıydın, yoksa kapısını mühürlü mü bırakırdın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="H127" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="I127" s="8" t="inlineStr">
         <is>
           <t>BBC / Wikipedia — Movile Cave Chemosynthesis Ecosystem (Movile Mağarası): https://en.wikipedia.org/wiki/Movile_Cave</t>
         </is>
       </c>
-      <c r="J127" s="5" t="n"/>
-      <c r="K127" s="5" t="n"/>
-      <c r="L127" s="5" t="n"/>
-      <c r="M127" s="5" t="n"/>
+      <c r="J127" s="8" t="n"/>
+      <c r="K127" s="8" t="n"/>
+      <c r="L127" s="8" t="n"/>
+      <c r="M127" s="8" t="n"/>
     </row>
     <row r="128" ht="42" customHeight="1">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>video_114.mp4</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C128" s="8" t="inlineStr">
         <is>
           <t>Dallol Volkanı: Dünya Üzerindeki En Asidik ve Renkli Cehennem! 🌋🧪 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D128" s="8" t="inlineStr">
         <is>
           <t>Şu gördüğün neon sarısı ve zümrüt yeşili göller başka bir gezegene değil, Dünya üzerindeki en tehlikeli cehenneme ait. Etiyopya'daki Danakil Çöküntüsü'nde yer alan Dallol Volkanı, deniz seviyesinin 48 metre altında kaynayan dev bir kimya laboratuvarı gibidir. Yerin altındaki kızgın magma, kalın tuz ve kükürt yataklarıyla buluştuğunda, yüzeye akü asidinden bile daha yakıcı kaynar sular ve zehirli klor gazları fışkırır. Burada maskesiz uzun süre nefes almak bile imkânsızdır. Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım!
 💬 Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇
@@ -7740,53 +7755,53 @@
 #bilgidozu #shorts #volkan #doğa #coğrafya #bilim</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E128" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #volkan #doğa #coğrafya #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F128" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, dallol volkanı, danakil çöküntüsü, etiyopya, asit gölleri, ekstrem doğa, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G128" s="8" t="inlineStr">
         <is>
           <t>Peki sen uzaylı bir gezegeni andıran bu yeri uzaktan dronelarla izlemeyi mi seçerdin, yoksa özel koruyucu kıyafetle yanına kadar yürümeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="H128" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="I128" s="8" t="inlineStr">
         <is>
           <t>Nature Ecology &amp; Evolution / Wikipedia — Dallol Hydrothermal System: https://en.wikipedia.org/wiki/Dallol_(hydrothermal_system)</t>
         </is>
       </c>
-      <c r="J128" s="5" t="n"/>
-      <c r="K128" s="5" t="n"/>
-      <c r="L128" s="5" t="n"/>
-      <c r="M128" s="5" t="n"/>
+      <c r="J128" s="8" t="n"/>
+      <c r="K128" s="8" t="n"/>
+      <c r="L128" s="8" t="n"/>
+      <c r="M128" s="8" t="n"/>
     </row>
     <row r="129" ht="42" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>video_115.mp4</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>Yerin 2.224 Metre Altında Ne Var? Dünya'nın En Derin Mağarası! 🧗‍♂️🌑 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>Yerin tam 2.224 metre altına, yani üst üste dizilmiş 7 Eyfel Kulesi derinliğine karanlık bir kuyudan indiğini hayal et. Kafkas Dağları'ndaki Krubera Mağarası, Dünya'nın bilinen en derin uçurumlarından biridir. Buraya inen mağaracıların en dibe ulaşması haftalar sürer ve içeride yeraltı şelaleleriyle buz gibi su tünelleri vardır. En şaşırtıcı olanı ise, 2.000 metre derinlikteki o dondurucu ve ışıksız sularda bile dış dünyayı hiç görmemiş şeffaf canlıların yaşamaya devam etmesidir. Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım!
 💬 Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇
@@ -7795,53 +7810,53 @@
 #bilgidozu #shorts #mağara #doğa #keşif #bilim</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
+      <c r="E129" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #mağara #doğa #keşif #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
+      <c r="F129" s="8" t="inlineStr">
         <is>
           <t>bilgidozu, krubera mağarası, dünyanın en derin mağarası, kafkas dağları, mağaracılık, doğa, coğrafya, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G129" s="5" t="inlineStr">
+      <c r="G129" s="8" t="inlineStr">
         <is>
           <t>Peki sana sınırsız ekipman verilse okyanusun en derin çukuruna dalmayı mı seçerdin, yoksa Dünya'nın en derin mağarasına inmeyi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H129" s="5" t="inlineStr">
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>Doğa ve Hayvanlar</t>
         </is>
       </c>
-      <c r="I129" s="5" t="inlineStr">
+      <c r="I129" s="8" t="inlineStr">
         <is>
           <t>National Geographic / Wikipedia — Krubera Cave (Dünya'nın En Derin Mağaraları): https://en.wikipedia.org/wiki/Krubera_Cave</t>
         </is>
       </c>
-      <c r="J129" s="5" t="n"/>
-      <c r="K129" s="5" t="n"/>
-      <c r="L129" s="5" t="n"/>
-      <c r="M129" s="5" t="n"/>
+      <c r="J129" s="8" t="n"/>
+      <c r="K129" s="8" t="n"/>
+      <c r="L129" s="8" t="n"/>
+      <c r="M129" s="8" t="n"/>
     </row>
     <row r="130" ht="42" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>video_116.mp4</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
+      <c r="C130" s="8" t="inlineStr">
         <is>
           <t>2.100 Yıllık Batıktan Çıkan İlk Analog Bilgisayar: Antikythera! ⚙️🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D130" s="8" t="inlineStr">
         <is>
           <t>Denizin dibinde iki bin yıl boyunca paslanmış bir Yunan batığından, modern saatler kadar karmaşık dişlilere sahip antik bir bilgisayar çıktığını biliyor muydun?
 💬 Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇
@@ -7850,53 +7865,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
+      <c r="E130" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
+      <c r="F130" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G130" s="5" t="inlineStr">
+      <c r="G130" s="8" t="inlineStr">
         <is>
           <t>Peki sence antik dünyada bunun gibi henüz keşfedemediğimiz başka yüksek teknolojiler de var mıdır, yoksa bu tek bir dahinin eseri miydi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="H130" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I130" s="5" t="inlineStr">
+      <c r="I130" s="8" t="inlineStr">
         <is>
           <t>Nature / Wikipedia — Antikythera Mechanism (2.100 Yıllık Antik Analog Bilgisayar): https://en.wikipedia.org/wiki/Antikythera_mechanism</t>
         </is>
       </c>
-      <c r="J130" s="5" t="n"/>
-      <c r="K130" s="5" t="n"/>
-      <c r="L130" s="5" t="n"/>
-      <c r="M130" s="5" t="n"/>
+      <c r="J130" s="8" t="n"/>
+      <c r="K130" s="8" t="n"/>
+      <c r="L130" s="8" t="n"/>
+      <c r="M130" s="8" t="n"/>
     </row>
     <row r="131" ht="42" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>video_117.mp4</t>
         </is>
       </c>
-      <c r="C131" s="5" t="inlineStr">
+      <c r="C131" s="8" t="inlineStr">
         <is>
           <t>Derinkuyu Yeraltı Şehri: 20 Bin Kişi Yerin Altında Nasıl Nefes Aldı? 🏺🕯️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="D131" s="8" t="inlineStr">
         <is>
           <t>Kapadokya'nın altında, yirmi bin insanın hayvanları ve erzaklarıyla birlikte haftalarca hiç yeryüzüne çıkmadan yaşayabildiği sekiz katlı dev bir yeraltı şehri var: Derinkuyu.
 💬 Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇
@@ -7905,53 +7920,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
+      <c r="E131" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F131" s="5" t="inlineStr">
+      <c r="F131" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G131" s="5" t="inlineStr">
+      <c r="G131" s="8" t="inlineStr">
         <is>
           <t>Peki sen tehlike anında haftalarca böyle bir yeraltı şehrinde yaşayabilir miydin, yoksa kapalı alanda daralır mıydın? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H131" s="5" t="inlineStr">
+      <c r="H131" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
+      <c r="I131" s="8" t="inlineStr">
         <is>
           <t>UNESCO / Wikipedia — Derinkuyu Underground City (Derinkuyu Yeraltı Şehri): https://en.wikipedia.org/wiki/Derinkuyu_underground_city</t>
         </is>
       </c>
-      <c r="J131" s="5" t="n"/>
-      <c r="K131" s="5" t="n"/>
-      <c r="L131" s="5" t="n"/>
-      <c r="M131" s="5" t="n"/>
+      <c r="J131" s="8" t="n"/>
+      <c r="K131" s="8" t="n"/>
+      <c r="L131" s="8" t="n"/>
+      <c r="M131" s="8" t="n"/>
     </row>
     <row r="132" ht="42" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>video_118.mp4</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C132" s="8" t="inlineStr">
         <is>
           <t>Voynich El Yazması: 600 Yıldır Kimsenin Okuyamadığı Şifreli Kitap! 📜🔍 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D132" s="8" t="inlineStr">
         <is>
           <t>Dünyanın en iyi şifre çözücüleri, dilbilimcileri ve yapay zekâları bir araya geldi ama altı yüz yıllık bu kitabın tek bir cümlesini bile okuyamadı: Voynich El Yazması.
 💬 Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇
@@ -7960,53 +7975,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E132" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F132" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="G132" s="8" t="inlineStr">
         <is>
           <t>Peki sence bu kitap unutulmuş gizli bir bilimin şifreli kaydı mı, yoksa tarihin en zekice kurgulanmış bilmecesi mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="H132" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Yale Beinecke Library / Wikipedia — Voynich Manuscript (Voynich El Yazması): https://en.wikipedia.org/wiki/Voynich_manuscript</t>
         </is>
       </c>
-      <c r="J132" s="5" t="n"/>
-      <c r="K132" s="5" t="n"/>
-      <c r="L132" s="5" t="n"/>
-      <c r="M132" s="5" t="n"/>
+      <c r="J132" s="8" t="n"/>
+      <c r="K132" s="8" t="n"/>
+      <c r="L132" s="8" t="n"/>
+      <c r="M132" s="8" t="n"/>
     </row>
     <row r="133" ht="42" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>video_119.mp4</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>Puma Punku H-Blokları: Jilet Bile Girmeyen Antik Taşların Sırrı! 🪨📐 #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>Deniz seviyesinden üç bin sekiz yüz metre yüksekte, aralarına jilet bile girmeyecek kadar kusursuz kesilmiş yüz tonluk taş bloklar düşün: Puma Punku.
 💬 Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇
@@ -8015,53 +8030,53 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E133" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
+      <c r="F133" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G133" s="5" t="inlineStr">
+      <c r="G133" s="8" t="inlineStr">
         <is>
           <t>Peki sence antik ustalar bu kusursuz taş işçiliğini sabırlı el aletleriyle mi başardı, yoksa bugün unuttuğumuz özel bir teknikleri mi vardı? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H133" s="5" t="inlineStr">
+      <c r="H133" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I133" s="8" t="inlineStr">
         <is>
           <t>UNESCO / Wikipedia — Pumapunku Andesite Megaliths (Puma Punku H-Blokları): https://en.wikipedia.org/wiki/Pumapunku</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n"/>
-      <c r="K133" s="5" t="n"/>
-      <c r="L133" s="5" t="n"/>
-      <c r="M133" s="5" t="n"/>
+      <c r="J133" s="8" t="n"/>
+      <c r="K133" s="8" t="n"/>
+      <c r="L133" s="8" t="n"/>
+      <c r="M133" s="8" t="n"/>
     </row>
     <row r="134" ht="42" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>ESKİ_STOK_ASKIDA</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>video_120.mp4</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C134" s="8" t="inlineStr">
         <is>
           <t>Babil'in Asma Bahçeleri Gerçekte Babil'de Değil Miydi? 🌿🏛️ #bilgidozu #shorts</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D134" s="8" t="inlineStr">
         <is>
           <t>Dünyanın Yedi Harikası'ndan biri sayılan Babil'in Asma Bahçeleri'nin aslında hiçbir zaman Babil'de olmadığını duysan ne derdin?
 💬 Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇
@@ -8070,85 +8085,200 @@
 #bilgidozu #shorts #tarih #arkeoloji #bilim</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E134" s="8" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #tarih #arkeoloji #bilim #dozdışı</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
+      <c r="F134" s="8" t="inlineStr">
         <is>
           <t>bilgi dozu, antik mühendislik, tarih, arkeoloji, gizemli yapılar, bilim, shorts, doz dışı</t>
         </is>
       </c>
-      <c r="G134" s="5" t="inlineStr">
+      <c r="G134" s="8" t="inlineStr">
         <is>
           <t>Peki sen geçmişe gidebilsen önce bu efsanevi Asma Bahçeleri'ni mi görmek isterdin, yoksa İskenderiye Kütüphanesi'ni mi? Yorumlarda buluşalım! 👇</t>
         </is>
       </c>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="H134" s="8" t="inlineStr">
         <is>
           <t>Tarih ve Antik Mühendislik</t>
         </is>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I134" s="8" t="inlineStr">
         <is>
           <t>Oxford University (Stephanie Dalley) / Wikipedia — Hanging Gardens of Babylon: https://en.wikipedia.org/wiki/Hanging_Gardens_of_Babylon</t>
         </is>
       </c>
-      <c r="J134" s="5" t="n"/>
-      <c r="K134" s="5" t="n"/>
-      <c r="L134" s="5" t="n"/>
-      <c r="M134" s="5" t="n"/>
+      <c r="J134" s="8" t="n"/>
+      <c r="K134" s="8" t="n"/>
+      <c r="L134" s="8" t="n"/>
+      <c r="M134" s="8" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>BEKLEMEDE</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="9" t="inlineStr">
         <is>
           <t>video_131.mp4</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Kâğıt Kesiği Neden Bu Kadar Acıtır? 🩹 #bilgidozu #shorts</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Kâğıt Kesiği Neden Bu Kadar Acıtır? 🩹</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>Küçücük bir kâğıt kesiği neden beklediğinden çok daha fazla can yakar? Parmak uçlarımız dokunma ve ağrıyı algılayan yoğun duyu sinirleriyle donatılmıştır. Üstelik çıplak gözle düz görünen kâğıt kenarı, mikroskobik ölçekte lifli ve düzensiz bir yapıya sahiptir; gün boyu ellerimizi kullanmaya devam etmemiz de hassaslaşan dokuyu tekrar tekrar uyarır.
-Senin de başına geldi mi? Yorumlarda buluşalım! 👇
+💬 Senin de başına geldi mi? En son ne zaman kâğıt kesiği yaşadın, yorumlara yaz! 👇
 📚 Kaynak: Dr. Hayley Goldbach (UCLA Dermatology) / BBC Future &amp; StatPearls
-🎨 Görseller temsilîdir (AI bilimsel canlandırma).</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
+🎨 Görseller temsilîdir (AI bilimsel canlandırma).
+#bilgidozu #shorts #insanvücudu #beyin #bilim</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
         <is>
           <t>#bilgidozu #shorts #insanvücudu #beyin #bilim</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="9" t="inlineStr">
         <is>
           <t>bilgi dozu, kağıt kesiği, insan vücudu, duyu sinirleri, bilim, ilginç bilgiler, shorts</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G135" s="9" t="inlineStr">
         <is>
           <t>Senin de başına geldi mi? En son ne zaman kâğıt kesiği yaşadın, yorumlara yaz! 👇</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H135" s="9" t="inlineStr">
         <is>
           <t>İnsan Vücudu ve Beyin</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I135" s="9" t="inlineStr">
         <is>
           <t>BBC Future (Dr. H. Goldbach, UCLA, 2016) &amp; StatPearls</t>
         </is>
       </c>
+      <c r="J135" s="9" t="n"/>
+      <c r="K135" s="9" t="n"/>
+      <c r="L135" s="9" t="n"/>
+      <c r="M135" s="9" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>video_132.mp4</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Baldırın İkinci Kalbin: Kanı Kalbe O Taşıyor! 🦵</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>Kalp kanı bacaklara kolayca gönderir; peki düşük basınçlı toplardamarlardaki kan yerçekimine karşı kalbe nasıl geri çıkar? Baldırımızdaki soleus ve gastroknemius kasları her adımda derin toplardamarları sıkıştırarak tek yönlü kapakçıklar yardımıyla kanı yukarı iter.
+💬 Bacaklarında akşamları ağırlık hissedenler 1 yazsın, hissetmeyenler 2! 👇
+📚 Kaynak: NCBI StatPearls (NBK430975, NBK534256) &amp; Cleveland Clinic (Dr. Teresa Wu)
+🎨 Görseller temsilîdir (AI bilimsel canlandırma).
+#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #insanvücudu #biyoloji #bilim</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>bilgi dozu, ikinci kalp, baldır kasları, kan dolaşımı, insan vücudu, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>Bacaklarında akşamları ağırlık hissedenler 1 yazsın, hissetmeyenler 2! 👇</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>Biyoloji ve Vücut</t>
+        </is>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>NCBI StatPearls (NBK430975, NBK534256) &amp; Cleveland Clinic (Dr. Teresa Wu)</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n"/>
+      <c r="K136" s="9" t="n"/>
+      <c r="L136" s="9" t="n"/>
+      <c r="M136" s="9" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>video_133.mp4</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Göz Kapağın Seğirirse Vücut Ne Anlatıyor? 👁</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>Gözünün altında başlayan istemsiz seğirme (oküler miyokimi) çoğu zaman korkutucu gelse de genellikle beynin değil, uykusuzluk, yoğun stres, fazla kafein ve ekran yorgunluğuyla geçici olarak aşırı uyarılan küçük sinir uçlarının eseridir.
+💬 Göz kapağı seğirmesi daha önce yaşayanlar 1, ilk kez duyanlar 2 yazsın! 👇
+📚 Kaynak: Mayo Clinic &amp; Cleveland Clinic — Eyelid Myokymia
+🎨 Görseller temsilîdir (AI bilimsel canlandırma).
+#bilgidozu #shorts #beyin #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>#bilgidozu #shorts #beyin #insanvücudu #bilim</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>bilgi dozu, göz seğirmesi, miyokimi, beyin ve psikoloji, insan vücudu, bilim, shorts</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>Göz kapağı seğirmesi daha önce yaşayanlar 1, ilk kez duyanlar 2 yazsın! 👇</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>Beyin ve Psikoloji</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>Mayo Clinic &amp; Cleveland Clinic — Eyelid Myokymia</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n"/>
+      <c r="K137" s="9" t="n"/>
+      <c r="L137" s="9" t="n"/>
+      <c r="M137" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
